--- a/data/SVGYO (TRY).xlsx
+++ b/data/SVGYO (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:G108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -411,6 +411,7 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,18 +419,21 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -443,19 +447,22 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>707117289</v>
+        <v>599014365</v>
       </c>
       <c r="C3">
-        <v>49448622</v>
+        <v>756710263.3411531</v>
       </c>
       <c r="D3">
-        <v>151532751.2331475</v>
+        <v>52916993</v>
       </c>
       <c r="E3">
-        <v>237247234.2695945</v>
+        <v>162160351.43562227</v>
       </c>
       <c r="F3">
-        <v>2539454.9500692966</v>
+        <v>253886335.28532648</v>
+      </c>
+      <c r="G3">
+        <v>2717557.120866737</v>
       </c>
     </row>
     <row r="4">
@@ -478,19 +485,22 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>31693579</v>
+        <v>26274534</v>
       </c>
       <c r="C7">
-        <v>21233739</v>
+        <v>33916376.93547278</v>
       </c>
       <c r="D7">
-        <v>19690486.537344866</v>
+        <v>22723091</v>
       </c>
       <c r="E7">
-        <v>2896534.1996772788</v>
+        <v>21071459.409599677</v>
       </c>
       <c r="F7">
-        <v>3615244.0444581048</v>
+        <v>3099679.7718156907</v>
+      </c>
+      <c r="G7">
+        <v>3868795.6234152094</v>
       </c>
     </row>
     <row r="8">
@@ -511,13 +521,16 @@
         <v>232831</v>
       </c>
       <c r="C10">
-        <v>62030</v>
+        <v>249160.37277655082</v>
       </c>
       <c r="D10">
-        <v>54725.088560476055</v>
+        <v>66380</v>
       </c>
       <c r="E10">
-        <v>50612.81139029048</v>
+        <v>58563.178726020036</v>
+      </c>
+      <c r="F10">
+        <v>54162.491048331336</v>
       </c>
     </row>
     <row r="11">
@@ -555,19 +568,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>37951365</v>
+        <v>66716482</v>
       </c>
       <c r="C17">
-        <v>41155604</v>
+        <v>40613046.59078449</v>
       </c>
       <c r="D17">
-        <v>31130193.47621853</v>
+        <v>44042290</v>
       </c>
       <c r="E17">
-        <v>9574062.413435899</v>
+        <v>33313478.92308481</v>
       </c>
       <c r="F17">
-        <v>3658726.1210175673</v>
+        <v>10245529.847475862</v>
+      </c>
+      <c r="G17">
+        <v>3915327.272571268</v>
       </c>
     </row>
     <row r="18">
@@ -580,7 +596,13 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>4600</v>
+        <v>90315</v>
+      </c>
+      <c r="C19">
+        <v>4922.616467618718</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -593,16 +615,19 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>46337686</v>
+        <v>54002978</v>
       </c>
       <c r="C21">
-        <v>43501199</v>
+        <v>49587533.95107507</v>
       </c>
       <c r="D21">
-        <v>31334347.074678347</v>
+        <v>46552406</v>
       </c>
       <c r="E21">
-        <v>12102513.143087251</v>
+        <v>33531950.63302001</v>
+      </c>
+      <c r="F21">
+        <v>12951310.977768103</v>
       </c>
     </row>
     <row r="22">
@@ -620,19 +645,22 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>823337350</v>
+        <v>746331505</v>
       </c>
       <c r="C24">
-        <v>155401194</v>
+        <v>881081303.8077296</v>
       </c>
       <c r="D24">
-        <v>233742503.40994972</v>
+        <v>166301160</v>
       </c>
       <c r="E24">
-        <v>261870956.8371852</v>
+        <v>250135803.5800528</v>
       </c>
       <c r="F24">
-        <v>9813425.11554497</v>
+        <v>280237018.3734344</v>
+      </c>
+      <c r="G24">
+        <v>10501680.016853215</v>
       </c>
     </row>
     <row r="25">
@@ -665,19 +693,22 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B30">
-        <v>266747</v>
+        <v>316426</v>
       </c>
       <c r="C30">
-        <v>266746</v>
+        <v>285455.03801910655</v>
       </c>
       <c r="D30">
-        <v>204841.3622359393</v>
+        <v>285456</v>
       </c>
       <c r="E30">
-        <v>204835.8601257303</v>
+        <v>219207.7093461056</v>
       </c>
       <c r="F30">
-        <v>442159.480191356</v>
+        <v>219201.82135081835</v>
+      </c>
+      <c r="G30">
+        <v>473169.8996747177</v>
       </c>
     </row>
     <row r="31">
@@ -700,10 +731,13 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B34">
-        <v>970499300</v>
+        <v>1110451545</v>
       </c>
       <c r="C34">
-        <v>927027870</v>
+        <v>1038564312.1722693</v>
+      </c>
+      <c r="D34">
+        <v>992050324</v>
       </c>
     </row>
     <row r="35">
@@ -721,19 +755,22 @@
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
       <c r="B37">
-        <v>3430832371</v>
+        <v>3671473614</v>
       </c>
       <c r="C37">
-        <v>3430832371</v>
+        <v>3671450418.939994</v>
       </c>
       <c r="D37">
-        <v>3459521881.971752</v>
+        <v>3671473614</v>
       </c>
       <c r="E37">
-        <v>3550071886.8623996</v>
+        <v>3702152040.495967</v>
       </c>
       <c r="F37">
-        <v>4076590360.1229186</v>
+        <v>3799052680.7606745</v>
+      </c>
+      <c r="G37">
+        <v>4362498008.364522</v>
       </c>
     </row>
     <row r="38">
@@ -746,19 +783,22 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>2609820</v>
+        <v>2719027</v>
       </c>
       <c r="C39">
-        <v>2709775</v>
+        <v>2792857.1542436266</v>
       </c>
       <c r="D39">
-        <v>2769078.9171084873</v>
+        <v>2899840</v>
       </c>
       <c r="E39">
-        <v>3411665.9667261452</v>
+        <v>2963285.5385856624</v>
       </c>
       <c r="F39">
-        <v>112224.34108831573</v>
+        <v>3650939.797787056</v>
+      </c>
+      <c r="G39">
+        <v>120095.08467587021</v>
       </c>
     </row>
     <row r="40">
@@ -770,25 +810,34 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
+      <c r="B41">
+        <v>628239</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>360555807</v>
+        <v>465251896</v>
       </c>
       <c r="C42">
-        <v>302693611</v>
+        <v>385843033.2682079</v>
       </c>
       <c r="D42">
-        <v>242676489.93686733</v>
+        <v>323924775</v>
       </c>
       <c r="E42">
-        <v>118006843.23522498</v>
+        <v>259696366.44937637</v>
       </c>
       <c r="F42">
-        <v>2072422.6304672626</v>
+        <v>126283136.91335195</v>
+      </c>
+      <c r="G42">
+        <v>2217769.9496964887</v>
       </c>
     </row>
     <row r="43">
@@ -810,14 +859,14 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
-      <c r="D46">
-        <v>845702523.1283115</v>
-      </c>
       <c r="E46">
-        <v>668299812.5618649</v>
+        <v>905015036.3169839</v>
       </c>
       <c r="F46">
-        <v>551198568.2484667</v>
+        <v>715170361.4398997</v>
+      </c>
+      <c r="G46">
+        <v>589856336.7364701</v>
       </c>
     </row>
     <row r="47">
@@ -825,19 +874,22 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>4764764045</v>
+        <v>5250840747</v>
       </c>
       <c r="C47">
-        <v>4663530373</v>
+        <v>5098936076.572734</v>
       </c>
       <c r="D47">
-        <v>4550874815.316276</v>
+        <v>4990634009</v>
       </c>
       <c r="E47">
-        <v>4339995044.486341</v>
+        <v>4870045936.510259</v>
       </c>
       <c r="F47">
-        <v>4630415734.8231325</v>
+        <v>4644376320.733065</v>
+      </c>
+      <c r="G47">
+        <v>4955165380.035039</v>
       </c>
     </row>
     <row r="48">
@@ -845,19 +897,22 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>5588101395</v>
+        <v>5997172252</v>
       </c>
       <c r="C48">
-        <v>4818931567</v>
+        <v>5980017380.380464</v>
       </c>
       <c r="D48">
-        <v>4784617320.927069</v>
+        <v>5156935169</v>
       </c>
       <c r="E48">
-        <v>4601866002.423948</v>
+        <v>5120181742.445509</v>
       </c>
       <c r="F48">
-        <v>4640229157.737833</v>
+        <v>4924613340.284098</v>
+      </c>
+      <c r="G48">
+        <v>4965667057.696693</v>
       </c>
     </row>
     <row r="49">
@@ -870,19 +925,22 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>3222978</v>
+        <v>2443143</v>
       </c>
       <c r="C50">
-        <v>3296834</v>
+        <v>3449018.3864288786</v>
       </c>
       <c r="D50">
-        <v>3134893.316884233</v>
+        <v>3528077</v>
       </c>
       <c r="E50">
-        <v>507434.3148665147</v>
+        <v>3354755.9708526502</v>
       </c>
       <c r="F50">
-        <v>101933.19415345474</v>
+        <v>543022.7205645059</v>
+      </c>
+      <c r="G50">
+        <v>109082.17829060268</v>
       </c>
     </row>
     <row r="51">
@@ -895,19 +953,22 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>24132563</v>
+        <v>45398281</v>
       </c>
       <c r="C52">
-        <v>41557107</v>
+        <v>25825076.528183952</v>
       </c>
       <c r="D52">
-        <v>39736973.91069675</v>
+        <v>44471956</v>
       </c>
       <c r="E52">
-        <v>2782719.74873857</v>
+        <v>42523887.423072</v>
       </c>
       <c r="F52">
-        <v>362197.3125243677</v>
+        <v>2977883.056501806</v>
+      </c>
+      <c r="G52">
+        <v>387599.6641651513</v>
       </c>
     </row>
     <row r="53">
@@ -920,19 +981,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>1716481</v>
+        <v>2882425</v>
       </c>
       <c r="C54">
-        <v>1372859</v>
+        <v>1836864.7036857924</v>
       </c>
       <c r="D54">
-        <v>1487585.7296029734</v>
+        <v>1469152</v>
       </c>
       <c r="E54">
-        <v>1079855.153833238</v>
+        <v>1591916.0890300442</v>
       </c>
       <c r="F54">
-        <v>372425.7354028464</v>
+        <v>1155589.731065748</v>
+      </c>
+      <c r="G54">
+        <v>398545.44740414416</v>
       </c>
     </row>
     <row r="55">
@@ -940,19 +1004,22 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>1118725</v>
+        <v>366130</v>
       </c>
       <c r="C55">
-        <v>1174889</v>
+        <v>1197185.6755949457</v>
       </c>
       <c r="D55">
-        <v>1112386.9306548052</v>
+        <v>1257298</v>
       </c>
       <c r="E55">
-        <v>101843481.14607541</v>
+        <v>1190403.092001127</v>
       </c>
       <c r="F55">
-        <v>19720597.385674484</v>
+        <v>108986173.34984507</v>
+      </c>
+      <c r="G55">
+        <v>21103682.052608665</v>
       </c>
     </row>
     <row r="56">
@@ -980,24 +1047,27 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>13284293</v>
+        <v>24857381</v>
       </c>
       <c r="C60">
-        <v>85543</v>
+        <v>14215973.800537406</v>
       </c>
       <c r="D60">
-        <v>2884212.7740753074</v>
+        <v>91543</v>
+      </c>
+      <c r="E60">
+        <v>3086494.1951694293</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="C61">
-        <v>468067</v>
-      </c>
       <c r="D61">
-        <v>564439.4778975887</v>
+        <v>500898</v>
+      </c>
+      <c r="E61">
+        <v>604025.8845375613</v>
       </c>
     </row>
     <row r="62">
@@ -1005,7 +1075,13 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>603047</v>
+        <v>636085</v>
+      </c>
+      <c r="C62">
+        <v>645341.1071626229</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1028,19 +1104,22 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>44078087</v>
+        <v>76583445</v>
       </c>
       <c r="C66">
-        <v>47955299</v>
+        <v>47169460.2015936</v>
       </c>
       <c r="D66">
-        <v>48920492.13981166</v>
+        <v>51318924</v>
       </c>
       <c r="E66">
-        <v>106213490.36351374</v>
+        <v>52351482.65466281</v>
       </c>
       <c r="F66">
-        <v>20557154.728177194</v>
+        <v>113662668.85797712</v>
+      </c>
+      <c r="G66">
+        <v>21998910.52006762</v>
       </c>
     </row>
     <row r="67">
@@ -1108,16 +1187,19 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B79">
-        <v>639771830</v>
+        <v>645316807</v>
       </c>
       <c r="C79">
-        <v>609592318</v>
+        <v>684641596.9296876</v>
       </c>
       <c r="D79">
-        <v>560900154.1706381</v>
+        <v>652349596</v>
       </c>
       <c r="E79">
-        <v>310851482.50148696</v>
+        <v>600238333.8283176</v>
+      </c>
+      <c r="F79">
+        <v>332652744.9446764</v>
       </c>
     </row>
     <row r="80">
@@ -1125,7 +1207,13 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>673242</v>
+        <v>868198</v>
+      </c>
+      <c r="C80">
+        <v>720459.1643244699</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1138,19 +1226,22 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>670327067</v>
+        <v>765461645</v>
       </c>
       <c r="C82">
-        <v>704113264</v>
+        <v>717339795.3705992</v>
       </c>
       <c r="D82">
-        <v>686739134.6435981</v>
+        <v>753500315</v>
       </c>
       <c r="E82">
-        <v>585052103.8004707</v>
+        <v>734902907.2075661</v>
       </c>
       <c r="F82">
-        <v>528938937.37436503</v>
+        <v>626084156.6485158</v>
+      </c>
+      <c r="G82">
+        <v>566035548.5834337</v>
       </c>
     </row>
     <row r="83">
@@ -1163,19 +1254,22 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>1310772139</v>
+        <v>1411646650</v>
       </c>
       <c r="C84">
-        <v>1313705582</v>
+        <v>1402701851.4646113</v>
       </c>
       <c r="D84">
-        <v>1247639288.8142362</v>
+        <v>1405849911</v>
       </c>
       <c r="E84">
-        <v>895903586.3019577</v>
+        <v>1335141241.0358837</v>
       </c>
       <c r="F84">
-        <v>528938937.37436503</v>
+        <v>958736901.5931923</v>
+      </c>
+      <c r="G84">
+        <v>566035548.5834337</v>
       </c>
     </row>
     <row r="85">
@@ -1188,19 +1282,22 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>4233251169</v>
+        <v>4508942157</v>
       </c>
       <c r="C86">
-        <v>3457270686</v>
+        <v>4530146068.714258</v>
       </c>
       <c r="D86">
-        <v>3488057539.973021</v>
+        <v>3699766334</v>
       </c>
       <c r="E86">
-        <v>3599748924.6580553</v>
+        <v>3732689018.754963</v>
       </c>
       <c r="F86">
-        <v>4090733065.635291</v>
+        <v>3852213768.6553297</v>
+      </c>
+      <c r="G86">
+        <v>4377632598.593193</v>
       </c>
     </row>
     <row r="87">
@@ -1211,15 +1308,18 @@
         <v>1083000000</v>
       </c>
       <c r="C87">
+        <v>1083000000</v>
+      </c>
+      <c r="D87">
         <v>874600000</v>
-      </c>
-      <c r="D87">
-        <v>912732560</v>
       </c>
       <c r="E87">
         <v>912732560</v>
       </c>
       <c r="F87">
+        <v>912732560</v>
+      </c>
+      <c r="G87">
         <v>882597955</v>
       </c>
     </row>
@@ -1228,19 +1328,22 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>1208994804</v>
+        <v>1369757097</v>
       </c>
       <c r="C88">
-        <v>1204954824</v>
+        <v>1369741601.275421</v>
       </c>
       <c r="D88">
-        <v>1166955896.4092069</v>
+        <v>1350816412</v>
       </c>
       <c r="E88">
-        <v>1166955896.4092069</v>
+        <v>1312812797.181851</v>
       </c>
       <c r="F88">
-        <v>1143249560.143275</v>
+        <v>1312812797.181851</v>
+      </c>
+      <c r="G88">
+        <v>1285330379.5497274</v>
       </c>
     </row>
     <row r="89">
@@ -1273,7 +1376,13 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>507471974</v>
+        <v>543066452</v>
+      </c>
+      <c r="C94">
+        <v>543063020.8842126</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1300,6 +1409,12 @@
       <c r="A99" t="str">
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
+      <c r="B99">
+        <v>4298028</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -1321,19 +1436,22 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>1377715862</v>
+        <v>1461712744</v>
       </c>
       <c r="C103">
-        <v>1519962795</v>
+        <v>1474340606.5175474</v>
       </c>
       <c r="D103">
-        <v>1520060469.34927</v>
+        <v>1626574165</v>
       </c>
       <c r="E103">
-        <v>1625259478.4316096</v>
+        <v>1626668412.6510773</v>
       </c>
       <c r="F103">
-        <v>1808556649.1839197</v>
+        <v>1739245450.5827937</v>
+      </c>
+      <c r="G103">
+        <v>1935397987.8030634</v>
       </c>
     </row>
     <row r="104">
@@ -1341,19 +1459,22 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>56068529</v>
+        <v>47107836</v>
       </c>
       <c r="C104">
-        <v>-142246933</v>
+        <v>60000840.037077755</v>
       </c>
       <c r="D104">
-        <v>-111691385.78545593</v>
+        <v>-152224243</v>
       </c>
       <c r="E104">
-        <v>-105199010.18276146</v>
+        <v>-119524751.07796535</v>
       </c>
       <c r="F104">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="G104">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="105">
@@ -1366,19 +1487,22 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>4233251169</v>
+        <v>4508942157</v>
       </c>
       <c r="C106">
-        <v>3457270686</v>
+        <v>4530146068.714258</v>
       </c>
       <c r="D106">
-        <v>3488057539.973021</v>
+        <v>3699766334</v>
       </c>
       <c r="E106">
-        <v>3599748924.6580553</v>
+        <v>3732689018.754963</v>
       </c>
       <c r="F106">
-        <v>4090733065.635291</v>
+        <v>3852213768.6553297</v>
+      </c>
+      <c r="G106">
+        <v>4377632598.593193</v>
       </c>
     </row>
     <row r="107">
@@ -1386,36 +1510,45 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>5588101395</v>
+        <v>5997172252</v>
       </c>
       <c r="C107">
-        <v>4818931567</v>
+        <v>5980017380.380464</v>
       </c>
       <c r="D107">
-        <v>4784617320.927069</v>
+        <v>5156935169</v>
       </c>
       <c r="E107">
-        <v>4601866002.423948</v>
+        <v>5120181742.445509</v>
       </c>
       <c r="F107">
-        <v>4640229157.737833</v>
+        <v>4924613340.284098</v>
+      </c>
+      <c r="G107">
+        <v>4965667057.696693</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B108">
+        <v>6059555</v>
+      </c>
+      <c r="C108">
+        <v>14015384.670420045</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:J50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1425,6 +1558,8 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1432,24 +1567,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1463,25 +1604,31 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>12575523</v>
+        <v>33860206</v>
       </c>
       <c r="C3">
-        <v>88424105.05021529</v>
+        <v>13457580</v>
       </c>
       <c r="D3">
-        <v>70428411.51209919</v>
+        <v>94625642.5336168</v>
       </c>
       <c r="E3">
-        <v>17912002</v>
+        <v>75367838.76036678</v>
       </c>
       <c r="F3">
-        <v>89653198.34093463</v>
+        <v>47019675</v>
       </c>
       <c r="G3">
-        <v>63520282.15652827</v>
+        <v>19168364</v>
       </c>
       <c r="H3">
-        <v>20927882.51236955</v>
+        <v>95940937.07125477</v>
+      </c>
+      <c r="I3">
+        <v>67975214.55902468</v>
+      </c>
+      <c r="J3">
+        <v>22395638.93212612</v>
       </c>
     </row>
     <row r="4">
@@ -1503,37 +1650,37 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>12575523</v>
+        <v>33860206</v>
       </c>
       <c r="C8">
-        <v>88424105.05021529</v>
+        <v>13457580</v>
       </c>
       <c r="D8">
-        <v>70428411.51209919</v>
+        <v>94625642.5336168</v>
       </c>
       <c r="E8">
-        <v>17912002</v>
+        <v>75367838.76036678</v>
       </c>
       <c r="F8">
-        <v>89653198.34093463</v>
+        <v>47019675</v>
       </c>
       <c r="G8">
-        <v>63520282.15652827</v>
+        <v>19168364</v>
       </c>
       <c r="H8">
-        <v>20927882.51236955</v>
+        <v>95940937.07125477</v>
+      </c>
+      <c r="I8">
+        <v>67975214.55902468</v>
+      </c>
+      <c r="J8">
+        <v>22395638.93212612</v>
       </c>
     </row>
     <row r="9">
@@ -1561,25 +1708,31 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>12575523</v>
+        <v>33860206</v>
       </c>
       <c r="C13">
-        <v>88424105.05021529</v>
+        <v>13457580</v>
       </c>
       <c r="D13">
-        <v>70428411.51209919</v>
+        <v>94625642.5336168</v>
       </c>
       <c r="E13">
-        <v>17912002</v>
+        <v>75367838.76036678</v>
       </c>
       <c r="F13">
-        <v>89653198.34093463</v>
+        <v>47019675</v>
       </c>
       <c r="G13">
-        <v>63520282.15652827</v>
+        <v>19168364</v>
       </c>
       <c r="H13">
-        <v>20927882.51236955</v>
+        <v>95940937.07125477</v>
+      </c>
+      <c r="I13">
+        <v>67975214.55902468</v>
+      </c>
+      <c r="J13">
+        <v>22395638.93212612</v>
       </c>
     </row>
     <row r="14"/>
@@ -1588,36 +1741,54 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-6782880</v>
+        <v>-18379139</v>
       </c>
       <c r="C15">
-        <v>-29845028.180359546</v>
+        <v>-7258636</v>
       </c>
       <c r="D15">
-        <v>-21569490.186370015</v>
+        <v>-31938179.825474482</v>
       </c>
       <c r="E15">
-        <v>-7452660</v>
+        <v>-23082245.128166385</v>
       </c>
       <c r="F15">
-        <v>-25605064.6389764</v>
+        <v>-15529136</v>
       </c>
       <c r="G15">
-        <v>-15681044.907387013</v>
+        <v>-7975395</v>
       </c>
       <c r="H15">
-        <v>-2580080.3310082615</v>
+        <v>-27400850.618753687</v>
+      </c>
+      <c r="I15">
+        <v>-16780819.541428685</v>
+      </c>
+      <c r="J15">
+        <v>-2761031.722869657</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
+      <c r="B16">
+        <v>-1826478</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="F16">
-        <v>-1744034.6847549852</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>-1512238.4846052928</v>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>-1866350.838972415</v>
+      </c>
+      <c r="I16">
+        <v>-1618297.8407140847</v>
       </c>
     </row>
     <row r="17">
@@ -1630,25 +1801,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>760665</v>
+        <v>2304206</v>
       </c>
       <c r="C18">
-        <v>4944210.53926867</v>
+        <v>814019</v>
       </c>
       <c r="D18">
-        <v>5967440.175675252</v>
+        <v>5290967.873908256</v>
       </c>
       <c r="E18">
-        <v>425562</v>
+        <v>6385960.712675768</v>
       </c>
       <c r="F18">
-        <v>1973763.191888146</v>
+        <v>769680</v>
       </c>
       <c r="G18">
-        <v>30454.180006659324</v>
+        <v>455411</v>
       </c>
       <c r="H18">
-        <v>43116217.04238347</v>
+        <v>2112191.1286017983</v>
+      </c>
+      <c r="I18">
+        <v>32590.05391491433</v>
+      </c>
+      <c r="J18">
+        <v>46140130.442230366</v>
       </c>
     </row>
     <row r="19">
@@ -1656,25 +1833,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-6093478</v>
+        <v>-13630971</v>
       </c>
       <c r="C19">
-        <v>-119357326.28221875</v>
+        <v>-6520879</v>
       </c>
       <c r="D19">
-        <v>-90899732.22059439</v>
+        <v>-127728334.75821532</v>
       </c>
       <c r="E19">
-        <v>-96307586</v>
+        <v>-97274895.37635429</v>
       </c>
       <c r="F19">
-        <v>-553345459.7397684</v>
+        <v>-74952032</v>
       </c>
       <c r="G19">
-        <v>-672724998.0409008</v>
+        <v>-103062675</v>
       </c>
       <c r="H19">
-        <v>-61820159.813351095</v>
+        <v>-592153798.3471813</v>
+      </c>
+      <c r="I19">
+        <v>-719905902.9423714</v>
+      </c>
+      <c r="J19">
+        <v>-66155855.81043978</v>
       </c>
     </row>
     <row r="20">
@@ -1687,25 +1870,31 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>459830</v>
+        <v>2327824</v>
       </c>
       <c r="C21">
-        <v>-55834038.873094335</v>
+        <v>492084</v>
       </c>
       <c r="D21">
-        <v>-36073370.71918995</v>
+        <v>-59749904.17616475</v>
       </c>
       <c r="E21">
-        <v>-85422682</v>
+        <v>-38603341.031478114</v>
       </c>
       <c r="F21">
-        <v>-489067598.63109905</v>
+        <v>-42691813</v>
       </c>
       <c r="G21">
-        <v>-626367546.1967802</v>
+        <v>-91414295</v>
       </c>
       <c r="H21">
-        <v>-356140.5896063315</v>
+        <v>-523367872.78265</v>
+      </c>
+      <c r="I21">
+        <v>-670297216.8891736</v>
+      </c>
+      <c r="J21">
+        <v>-381118.1589529494</v>
       </c>
     </row>
     <row r="22"/>
@@ -1724,28 +1913,46 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>29495948</v>
+        <v>99369573</v>
       </c>
       <c r="C25">
-        <v>84389322.90147899</v>
+        <v>31564817</v>
       </c>
       <c r="D25">
-        <v>80098721.23899859</v>
+        <v>90307884.91435085</v>
       </c>
       <c r="E25">
-        <v>29093967</v>
+        <v>85716366.13180341</v>
       </c>
       <c r="F25">
-        <v>1942345.042172875</v>
+        <v>61994578</v>
+      </c>
+      <c r="G25">
+        <v>31134640</v>
       </c>
       <c r="H25">
-        <v>22793.041751686887</v>
+        <v>2078569.4979125583</v>
+      </c>
+      <c r="J25">
+        <v>24391.609276951058</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>-26522</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1782,25 +1989,31 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>29955778</v>
+        <v>101670875</v>
       </c>
       <c r="C33">
-        <v>28555284.02838466</v>
+        <v>32056901</v>
       </c>
       <c r="D33">
-        <v>44025350.51980864</v>
+        <v>30557980.738186106</v>
       </c>
       <c r="E33">
-        <v>-56328715</v>
+        <v>47113025.10032529</v>
       </c>
       <c r="F33">
-        <v>-487125253.5889262</v>
+        <v>19302765</v>
       </c>
       <c r="G33">
-        <v>-626367546.1967802</v>
+        <v>-60279655</v>
       </c>
       <c r="H33">
-        <v>-333347.5478546446</v>
+        <v>-521289303.28473747</v>
+      </c>
+      <c r="I33">
+        <v>-670297216.8891736</v>
+      </c>
+      <c r="J33">
+        <v>-356726.54967599834</v>
       </c>
     </row>
     <row r="34"/>
@@ -1808,11 +2021,23 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
       <c r="F35">
-        <v>7039318.370127523</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>1942356.046393293</v>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>7533014.028174066</v>
+      </c>
+      <c r="I35">
+        <v>2078581.2739031329</v>
       </c>
     </row>
     <row r="36">
@@ -1820,25 +2045,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-331957</v>
+        <v>-746899</v>
       </c>
       <c r="C36">
-        <v>-1110690.079866358</v>
+        <v>-355241</v>
       </c>
       <c r="D36">
-        <v>-810224.2430425712</v>
+        <v>-1188587.23425454</v>
       </c>
       <c r="E36">
-        <v>-124322</v>
+        <v>-867048.5220141895</v>
       </c>
       <c r="F36">
-        <v>-404924.4995631597</v>
+        <v>-406293</v>
       </c>
       <c r="G36">
-        <v>-1310349.5547074878</v>
+        <v>-133042</v>
       </c>
       <c r="H36">
-        <v>-319717.7204449795</v>
+        <v>-433323.4803677997</v>
+      </c>
+      <c r="I36">
+        <v>-1402249.629639116</v>
+      </c>
+      <c r="J36">
+        <v>-342140.8077504291</v>
       </c>
     </row>
     <row r="37">
@@ -1846,25 +2077,31 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-7341489</v>
+        <v>-41854810</v>
       </c>
       <c r="C37">
-        <v>-47917312.19300657</v>
+        <v>-7856427</v>
       </c>
       <c r="D37">
-        <v>-50915407.644187175</v>
+        <v>-51277945.67072203</v>
       </c>
       <c r="E37">
-        <v>-9973871</v>
+        <v>-54486309.59234691</v>
       </c>
       <c r="F37">
-        <v>-8221064.902076628</v>
+        <v>-16889232</v>
       </c>
       <c r="G37">
-        <v>-2035363.7173657534</v>
+        <v>-10673446</v>
       </c>
       <c r="H37">
-        <v>264214251.6545063</v>
+        <v>-8797641.188766234</v>
+      </c>
+      <c r="I37">
+        <v>-2178111.9462387627</v>
+      </c>
+      <c r="J37">
+        <v>282744657.8639193</v>
       </c>
     </row>
     <row r="38">
@@ -1872,25 +2109,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>22282332</v>
+        <v>59069166</v>
       </c>
       <c r="C38">
-        <v>-20472718.24448827</v>
+        <v>23845233</v>
       </c>
       <c r="D38">
-        <v>-7700281.3674211055</v>
+        <v>-21908552.166790463</v>
       </c>
       <c r="E38">
-        <v>-66426908</v>
+        <v>-8240333.014035808</v>
       </c>
       <c r="F38">
-        <v>-488711924.62043846</v>
+        <v>2007240</v>
       </c>
       <c r="G38">
-        <v>-627770903.4224601</v>
+        <v>-71086143</v>
       </c>
       <c r="H38">
-        <v>263561186.38620666</v>
+        <v>-522987253.9256974</v>
+      </c>
+      <c r="I38">
+        <v>-671798997.1911483</v>
+      </c>
+      <c r="J38">
+        <v>282045790.50649285</v>
       </c>
     </row>
     <row r="39"/>
@@ -1899,36 +2142,54 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>33786197</v>
+        <v>-11961330</v>
       </c>
       <c r="C40">
-        <v>-121776846.23395288</v>
+        <v>36155987</v>
       </c>
       <c r="D40">
-        <v>-103991104.41803482</v>
+        <v>-130317545.35781063</v>
       </c>
       <c r="E40">
-        <v>-35796792</v>
+        <v>-111284418.06392953</v>
       </c>
       <c r="F40">
-        <v>383512914.43767697</v>
+        <v>-81235576</v>
       </c>
       <c r="G40">
-        <v>528938937.37436503</v>
+        <v>-38307607</v>
       </c>
       <c r="H40">
-        <v>-7232285.078110459</v>
+        <v>410410214.816382</v>
+      </c>
+      <c r="I40">
+        <v>566035548.5834337</v>
+      </c>
+      <c r="J40">
+        <v>-7739514.266091234</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
       <c r="C41">
-        <v>-2675888.5760770887</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>-2304073.5749074384</v>
+        <v>-2863559.3848064956</v>
+      </c>
+      <c r="E41">
+        <v>-2465667.504879236</v>
+      </c>
+      <c r="F41">
+        <v>-2001229</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1936,25 +2197,31 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>33786197</v>
+        <v>-11961330</v>
       </c>
       <c r="C42">
-        <v>-119100957.65787579</v>
+        <v>36155987</v>
       </c>
       <c r="D42">
-        <v>-101687030.84312738</v>
+        <v>-127453985.97300415</v>
       </c>
       <c r="E42">
-        <v>-35796792</v>
+        <v>-108818750.5590503</v>
       </c>
       <c r="F42">
-        <v>383512914.43767697</v>
+        <v>-79234347</v>
       </c>
       <c r="G42">
-        <v>528938937.37436503</v>
+        <v>-38307607</v>
       </c>
       <c r="H42">
-        <v>-7232285.078110459</v>
+        <v>410410214.816382</v>
+      </c>
+      <c r="I42">
+        <v>566035548.5834337</v>
+      </c>
+      <c r="J42">
+        <v>-7739514.266091234</v>
       </c>
     </row>
     <row r="43">
@@ -1962,25 +2229,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>56068529</v>
+        <v>47107836</v>
       </c>
       <c r="C43">
-        <v>-142249564.47844115</v>
+        <v>60001220</v>
       </c>
       <c r="D43">
-        <v>-111691385.78545593</v>
+        <v>-152226097.5246011</v>
       </c>
       <c r="E43">
-        <v>-102223700</v>
+        <v>-119524751.07796535</v>
       </c>
       <c r="F43">
-        <v>-105199010.18276146</v>
+        <v>-79228336</v>
       </c>
       <c r="G43">
-        <v>-98831966.04809512</v>
+        <v>-109393750</v>
       </c>
       <c r="H43">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="I43">
+        <v>-105763448.6077146</v>
+      </c>
+      <c r="J43">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="44">
@@ -1994,25 +2267,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>56068529</v>
+        <v>47107836</v>
       </c>
       <c r="C46">
-        <v>-142249564.47844115</v>
+        <v>60001220</v>
       </c>
       <c r="D46">
-        <v>-111691385.78545593</v>
+        <v>-152226097.5246011</v>
       </c>
       <c r="E46">
-        <v>-102223700</v>
+        <v>-119524751.07796535</v>
       </c>
       <c r="F46">
-        <v>-105199010.18276146</v>
+        <v>-79228336</v>
       </c>
       <c r="G46">
-        <v>-98831966.04809512</v>
+        <v>-109393750</v>
       </c>
       <c r="H46">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="I46">
+        <v>-105763448.6077146</v>
+      </c>
+      <c r="J46">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="47">
@@ -2022,7 +2301,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2031,25 +2316,31 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>56068529</v>
+        <v>47107836</v>
       </c>
       <c r="C48">
-        <v>-142249564.47844115</v>
+        <v>60001220</v>
       </c>
       <c r="D48">
-        <v>-111691385.78545593</v>
+        <v>-152226097.5246011</v>
       </c>
       <c r="E48">
-        <v>-102223700</v>
+        <v>-119524751.07796535</v>
       </c>
       <c r="F48">
-        <v>-105199010.18276146</v>
+        <v>-79228336</v>
       </c>
       <c r="G48">
-        <v>-98831966.04809512</v>
+        <v>-109393750</v>
       </c>
       <c r="H48">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="I48">
+        <v>-105763448.6077146</v>
+      </c>
+      <c r="J48">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="49"/>
@@ -2058,37 +2349,43 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>99955</v>
+        <v>243988</v>
       </c>
       <c r="C50">
-        <v>391842.6823303082</v>
+        <v>106965.24543931065</v>
       </c>
       <c r="D50">
-        <v>289858.8687629309</v>
+        <v>419324.18277284026</v>
       </c>
       <c r="E50">
-        <v>94457</v>
+        <v>310187.8349255949</v>
       </c>
       <c r="F50">
-        <v>192065.4623307066</v>
+        <v>204260</v>
       </c>
       <c r="G50">
-        <v>80784.18293220864</v>
+        <v>101081.64862649159</v>
       </c>
       <c r="H50">
-        <v>5287.527910821971</v>
+        <v>205535.78428911715</v>
+      </c>
+      <c r="I50">
+        <v>86449.90200548114</v>
+      </c>
+      <c r="J50">
+        <v>5658.363471044746</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:J50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2098,6 +2395,8 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2105,24 +2404,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2136,16 +2441,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>12575523</v>
+        <v>20402626</v>
       </c>
       <c r="C3">
-        <v>17995693.538116097</v>
+        <v>13457580</v>
+      </c>
+      <c r="D3">
+        <v>19257803.773250014</v>
       </c>
       <c r="E3">
-        <v>17912002</v>
+        <v>28348163.760366783</v>
       </c>
       <c r="F3">
-        <v>26132916.184406362</v>
+        <v>27851311</v>
+      </c>
+      <c r="G3">
+        <v>19168364</v>
+      </c>
+      <c r="H3">
+        <v>27965722.5122301</v>
       </c>
     </row>
     <row r="4">
@@ -2167,28 +2481,31 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>12575523</v>
+        <v>20402626</v>
       </c>
       <c r="C8">
-        <v>17995693.538116097</v>
+        <v>13457580</v>
+      </c>
+      <c r="D8">
+        <v>19257803.773250014</v>
       </c>
       <c r="E8">
-        <v>17912002</v>
+        <v>28348163.760366783</v>
       </c>
       <c r="F8">
-        <v>26132916.184406362</v>
+        <v>27851311</v>
+      </c>
+      <c r="G8">
+        <v>19168364</v>
+      </c>
+      <c r="H8">
+        <v>27965722.5122301</v>
       </c>
     </row>
     <row r="9">
@@ -2216,16 +2533,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>12575523</v>
+        <v>20402626</v>
       </c>
       <c r="C13">
-        <v>17995693.538116097</v>
+        <v>13457580</v>
+      </c>
+      <c r="D13">
+        <v>19257803.773250014</v>
       </c>
       <c r="E13">
-        <v>17912002</v>
+        <v>28348163.760366783</v>
       </c>
       <c r="F13">
-        <v>26132916.184406362</v>
+        <v>27851311</v>
+      </c>
+      <c r="G13">
+        <v>19168364</v>
+      </c>
+      <c r="H13">
+        <v>27965722.5122301</v>
       </c>
     </row>
     <row r="14"/>
@@ -2234,24 +2560,45 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-6782880</v>
+        <v>-11120503</v>
       </c>
       <c r="C15">
-        <v>-8275537.993989531</v>
+        <v>-7258636</v>
+      </c>
+      <c r="D15">
+        <v>-8855934.697308097</v>
       </c>
       <c r="E15">
-        <v>-7452660</v>
+        <v>-7553109.128166385</v>
       </c>
       <c r="F15">
-        <v>-9924019.731589386</v>
+        <v>-7553741</v>
+      </c>
+      <c r="G15">
+        <v>-7975395</v>
+      </c>
+      <c r="H15">
+        <v>-10620031.077325001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
+      <c r="B16">
+        <v>-1826478</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="F16">
-        <v>-231796.20014969236</v>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>-248052.9982583304</v>
       </c>
     </row>
     <row r="17">
@@ -2264,16 +2611,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>760665</v>
+        <v>1490187</v>
       </c>
       <c r="C18">
-        <v>-1023229.6364065828</v>
+        <v>814019</v>
+      </c>
+      <c r="D18">
+        <v>-1094992.8387675118</v>
       </c>
       <c r="E18">
-        <v>425562</v>
+        <v>5616280.712675768</v>
       </c>
       <c r="F18">
-        <v>1943309.0118814867</v>
+        <v>314269</v>
+      </c>
+      <c r="G18">
+        <v>455411</v>
+      </c>
+      <c r="H18">
+        <v>2079601.074686884</v>
       </c>
     </row>
     <row r="19">
@@ -2281,16 +2637,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-6093478</v>
+        <v>-7110092</v>
       </c>
       <c r="C19">
-        <v>-28457594.061624363</v>
+        <v>-6520879</v>
+      </c>
+      <c r="D19">
+        <v>-30453439.38186103</v>
       </c>
       <c r="E19">
-        <v>-96307586</v>
+        <v>-22322863.376354292</v>
       </c>
       <c r="F19">
-        <v>119379538.30113244</v>
+        <v>28110643</v>
+      </c>
+      <c r="G19">
+        <v>-103062675</v>
+      </c>
+      <c r="H19">
+        <v>127752104.59519005</v>
       </c>
     </row>
     <row r="20">
@@ -2303,16 +2668,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>459830</v>
+        <v>1835740</v>
       </c>
       <c r="C21">
-        <v>-19760668.153904386</v>
+        <v>492084</v>
+      </c>
+      <c r="D21">
+        <v>-21146563.14468663</v>
       </c>
       <c r="E21">
-        <v>-85422682</v>
+        <v>4088471.9685218856</v>
       </c>
       <c r="F21">
-        <v>137299947.56568116</v>
+        <v>48722482</v>
+      </c>
+      <c r="G21">
+        <v>-91414295</v>
+      </c>
+      <c r="H21">
+        <v>146929344.10652363</v>
       </c>
     </row>
     <row r="22"/>
@@ -2331,19 +2705,40 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>29495948</v>
+        <v>67804756</v>
       </c>
       <c r="C25">
-        <v>4290601.662480399</v>
+        <v>31564817</v>
+      </c>
+      <c r="D25">
+        <v>4591518.782547444</v>
       </c>
       <c r="E25">
-        <v>29093967</v>
+        <v>23721788.13180341</v>
+      </c>
+      <c r="F25">
+        <v>30859938</v>
+      </c>
+      <c r="G25">
+        <v>31134640</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>-26522</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2380,16 +2775,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>29955778</v>
+        <v>69613974</v>
       </c>
       <c r="C33">
-        <v>-15470066.491423983</v>
+        <v>32056901</v>
+      </c>
+      <c r="D33">
+        <v>-16555044.36213918</v>
       </c>
       <c r="E33">
-        <v>-56328715</v>
+        <v>27810260.100325286</v>
       </c>
       <c r="F33">
-        <v>139242292.607854</v>
+        <v>79582420</v>
+      </c>
+      <c r="G33">
+        <v>-60279655</v>
+      </c>
+      <c r="H33">
+        <v>149007913.60443616</v>
       </c>
     </row>
     <row r="34"/>
@@ -2397,8 +2801,20 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
       <c r="F35">
-        <v>5096962.32373423</v>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>5454432.754270934</v>
       </c>
     </row>
     <row r="36">
@@ -2406,16 +2822,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-331957</v>
+        <v>-391658</v>
       </c>
       <c r="C36">
-        <v>-300465.83682378684</v>
+        <v>-355241</v>
+      </c>
+      <c r="D36">
+        <v>-321538.71224035043</v>
       </c>
       <c r="E36">
-        <v>-124322</v>
+        <v>-460755.5220141895</v>
       </c>
       <c r="F36">
-        <v>905425.0551443282</v>
+        <v>-273251</v>
+      </c>
+      <c r="G36">
+        <v>-133042</v>
+      </c>
+      <c r="H36">
+        <v>968926.1492713164</v>
       </c>
     </row>
     <row r="37">
@@ -2423,16 +2848,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-7341489</v>
+        <v>-33998383</v>
       </c>
       <c r="C37">
-        <v>2998095.451180607</v>
+        <v>-7856427</v>
+      </c>
+      <c r="D37">
+        <v>3208363.9216248766</v>
       </c>
       <c r="E37">
-        <v>-9973871</v>
+        <v>-37597077.59234691</v>
       </c>
       <c r="F37">
-        <v>-6185701.184710875</v>
+        <v>-6215786</v>
+      </c>
+      <c r="G37">
+        <v>-10673446</v>
+      </c>
+      <c r="H37">
+        <v>-6619529.242527471</v>
       </c>
     </row>
     <row r="38">
@@ -2440,16 +2874,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>22282332</v>
+        <v>35223933</v>
       </c>
       <c r="C38">
-        <v>-12772436.877067164</v>
+        <v>23845233</v>
+      </c>
+      <c r="D38">
+        <v>-13668219.152754655</v>
       </c>
       <c r="E38">
-        <v>-66426908</v>
+        <v>-10247573.014035808</v>
       </c>
       <c r="F38">
-        <v>139058978.80202162</v>
+        <v>73093383</v>
+      </c>
+      <c r="G38">
+        <v>-71086143</v>
+      </c>
+      <c r="H38">
+        <v>148811743.2654509</v>
       </c>
     </row>
     <row r="39"/>
@@ -2458,24 +2901,48 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>33786197</v>
+        <v>-48117317</v>
       </c>
       <c r="C40">
-        <v>-17785741.81591806</v>
+        <v>36155987</v>
+      </c>
+      <c r="D40">
+        <v>-19033127.293881103</v>
       </c>
       <c r="E40">
-        <v>-35796792</v>
+        <v>-30048842.063929528</v>
       </c>
       <c r="F40">
-        <v>-145426022.93668807</v>
+        <v>-42927969</v>
+      </c>
+      <c r="G40">
+        <v>-38307607</v>
+      </c>
+      <c r="H40">
+        <v>-155625333.76705176</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
       <c r="C41">
-        <v>-371815.00116965035</v>
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>-397891.8799272594</v>
+      </c>
+      <c r="E41">
+        <v>-464438.5048792362</v>
+      </c>
+      <c r="F41">
+        <v>-2001229</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2483,16 +2950,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>33786197</v>
+        <v>-48117317</v>
       </c>
       <c r="C42">
-        <v>-17413926.814748406</v>
+        <v>36155987</v>
+      </c>
+      <c r="D42">
+        <v>-18635235.41395384</v>
       </c>
       <c r="E42">
-        <v>-35796792</v>
+        <v>-29584403.559050307</v>
       </c>
       <c r="F42">
-        <v>-145426022.93668807</v>
+        <v>-40926740</v>
+      </c>
+      <c r="G42">
+        <v>-38307607</v>
+      </c>
+      <c r="H42">
+        <v>-155625333.76705176</v>
       </c>
     </row>
     <row r="43">
@@ -2500,16 +2976,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>56068529</v>
+        <v>-12893384</v>
       </c>
       <c r="C43">
-        <v>-30558178.69298522</v>
+        <v>60001220</v>
+      </c>
+      <c r="D43">
+        <v>-32701346.446635753</v>
       </c>
       <c r="E43">
-        <v>-102223700</v>
+        <v>-40296415.07796535</v>
       </c>
       <c r="F43">
-        <v>-6367044.134666339</v>
+        <v>30165414</v>
+      </c>
+      <c r="G43">
+        <v>-109393750</v>
+      </c>
+      <c r="H43">
+        <v>-6813590.501600802</v>
       </c>
     </row>
     <row r="44">
@@ -2523,16 +3008,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>56068529</v>
+        <v>-12893384</v>
       </c>
       <c r="C46">
-        <v>-30558178.69298522</v>
+        <v>60001220</v>
+      </c>
+      <c r="D46">
+        <v>-32701346.446635753</v>
       </c>
       <c r="E46">
-        <v>-102223700</v>
+        <v>-40296415.07796535</v>
       </c>
       <c r="F46">
-        <v>-6367044.134666339</v>
+        <v>30165414</v>
+      </c>
+      <c r="G46">
+        <v>-109393750</v>
+      </c>
+      <c r="H46">
+        <v>-6813590.501600802</v>
       </c>
     </row>
     <row r="47">
@@ -2542,7 +3036,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -2551,16 +3051,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>56068529</v>
+        <v>-12893384</v>
       </c>
       <c r="C48">
-        <v>-30558178.69298522</v>
+        <v>60001220</v>
+      </c>
+      <c r="D48">
+        <v>-32701346.446635753</v>
       </c>
       <c r="E48">
-        <v>-102223700</v>
+        <v>-40296415.07796535</v>
       </c>
       <c r="F48">
-        <v>-6367044.134666339</v>
+        <v>30165414</v>
+      </c>
+      <c r="G48">
+        <v>-109393750</v>
+      </c>
+      <c r="H48">
+        <v>-6813590.501600802</v>
       </c>
     </row>
     <row r="49"/>
@@ -2569,28 +3078,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>99955</v>
+        <v>137022.75456068935</v>
       </c>
       <c r="C50">
-        <v>101983.81356737728</v>
+        <v>106965.24543931065</v>
+      </c>
+      <c r="D50">
+        <v>109136.34784724534</v>
       </c>
       <c r="E50">
-        <v>94457</v>
+        <v>105927.83492559491</v>
       </c>
       <c r="F50">
-        <v>111281.27939849795</v>
+        <v>103178.35137350841</v>
+      </c>
+      <c r="G50">
+        <v>101081.64862649159</v>
+      </c>
+      <c r="H50">
+        <v>119085.882283636</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:J50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2600,6 +3118,8 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2607,24 +3127,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2638,19 +3164,22 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>83087626.05021529</v>
+        <v>81466173.5336168</v>
       </c>
       <c r="C3">
-        <v>88424105.05021529</v>
+        <v>88914858.5336168</v>
       </c>
       <c r="D3">
-        <v>96561327.69650555</v>
-      </c>
-      <c r="F3">
-        <v>89653198.34093463</v>
+        <v>94625642.5336168</v>
+      </c>
+      <c r="E3">
+        <v>103333561.27259688</v>
       </c>
       <c r="H3">
-        <v>20927882.51236955</v>
+        <v>95940937.07125477</v>
+      </c>
+      <c r="J3">
+        <v>22395638.93212612</v>
       </c>
     </row>
     <row r="4">
@@ -2678,19 +3207,22 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>83087626.05021529</v>
+        <v>81466173.5336168</v>
       </c>
       <c r="C8">
-        <v>88424105.05021529</v>
+        <v>88914858.5336168</v>
       </c>
       <c r="D8">
-        <v>96561327.69650555</v>
-      </c>
-      <c r="F8">
-        <v>89653198.34093463</v>
+        <v>94625642.5336168</v>
+      </c>
+      <c r="E8">
+        <v>103333561.27259688</v>
       </c>
       <c r="H8">
-        <v>20927882.51236955</v>
+        <v>95940937.07125477</v>
+      </c>
+      <c r="J8">
+        <v>22395638.93212612</v>
       </c>
     </row>
     <row r="9">
@@ -2718,19 +3250,22 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>83087626.05021529</v>
+        <v>81466173.5336168</v>
       </c>
       <c r="C13">
-        <v>88424105.05021529</v>
+        <v>88914858.5336168</v>
       </c>
       <c r="D13">
-        <v>96561327.69650555</v>
-      </c>
-      <c r="F13">
-        <v>89653198.34093463</v>
+        <v>94625642.5336168</v>
+      </c>
+      <c r="E13">
+        <v>103333561.27259688</v>
       </c>
       <c r="H13">
-        <v>20927882.51236955</v>
+        <v>95940937.07125477</v>
+      </c>
+      <c r="J13">
+        <v>22395638.93212612</v>
       </c>
     </row>
     <row r="14"/>
@@ -2739,27 +3274,30 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-29175248.180359546</v>
+        <v>-34788182.825474486</v>
       </c>
       <c r="C15">
-        <v>-29845028.180359546</v>
+        <v>-31221420.825474482</v>
       </c>
       <c r="D15">
-        <v>-31493509.9179594</v>
-      </c>
-      <c r="F15">
-        <v>-25605064.6389764</v>
+        <v>-31938179.825474482</v>
+      </c>
+      <c r="E15">
+        <v>-33702276.20549139</v>
       </c>
       <c r="H15">
-        <v>-2580080.3310082615</v>
+        <v>-27400850.618753687</v>
+      </c>
+      <c r="J15">
+        <v>-2761031.722869657</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
-      <c r="F16">
-        <v>-1744034.6847549852</v>
+      <c r="H16">
+        <v>-1866350.838972415</v>
       </c>
     </row>
     <row r="17">
@@ -2772,19 +3310,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>5279313.53926867</v>
+        <v>6825493.873908256</v>
       </c>
       <c r="C18">
-        <v>4944210.53926867</v>
+        <v>5649575.873908256</v>
       </c>
       <c r="D18">
-        <v>7910749.187556739</v>
-      </c>
-      <c r="F18">
-        <v>1973763.191888146</v>
+        <v>5290967.873908256</v>
+      </c>
+      <c r="E18">
+        <v>8465561.787362652</v>
       </c>
       <c r="H18">
-        <v>43116217.04238347</v>
+        <v>2112191.1286017983</v>
+      </c>
+      <c r="J18">
+        <v>46140130.442230366</v>
       </c>
     </row>
     <row r="19">
@@ -2792,19 +3333,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-29143218.282218754</v>
+        <v>-66407273.75821532</v>
       </c>
       <c r="C19">
-        <v>-119357326.28221875</v>
+        <v>-31186538.758215323</v>
       </c>
       <c r="D19">
-        <v>28479806.08053805</v>
-      </c>
-      <c r="F19">
-        <v>-553345459.7397684</v>
+        <v>-127728334.75821532</v>
+      </c>
+      <c r="E19">
+        <v>30477209.218835756</v>
       </c>
       <c r="H19">
-        <v>-61820159.813351095</v>
+        <v>-592153798.3471813</v>
+      </c>
+      <c r="J19">
+        <v>-66155855.81043978</v>
       </c>
     </row>
     <row r="20">
@@ -2817,19 +3361,22 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>30048473.126905665</v>
+        <v>-14730267.176164746</v>
       </c>
       <c r="C21">
-        <v>-55834038.873094335</v>
+        <v>32156474.823835254</v>
       </c>
       <c r="D21">
-        <v>101226576.84649122</v>
-      </c>
-      <c r="F21">
-        <v>-489067598.63109905</v>
+        <v>-59749904.17616475</v>
+      </c>
+      <c r="E21">
+        <v>108326003.07504553</v>
       </c>
       <c r="H21">
-        <v>-356140.5896063315</v>
+        <v>-523367872.78265</v>
+      </c>
+      <c r="J21">
+        <v>-381118.1589529494</v>
       </c>
     </row>
     <row r="22"/>
@@ -2848,16 +3395,19 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>84791303.90147899</v>
+        <v>127682879.91435085</v>
       </c>
       <c r="C25">
-        <v>84389322.90147899</v>
-      </c>
-      <c r="F25">
-        <v>1942345.042172875</v>
+        <v>90738061.91435085</v>
+      </c>
+      <c r="D25">
+        <v>90307884.91435085</v>
       </c>
       <c r="H25">
-        <v>22793.041751686887</v>
+        <v>2078569.4979125583</v>
+      </c>
+      <c r="J25">
+        <v>24391.609276951058</v>
       </c>
     </row>
     <row r="26">
@@ -2900,19 +3450,22 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>114839777.02838466</v>
+        <v>112926090.7381861</v>
       </c>
       <c r="C33">
-        <v>28555284.02838466</v>
+        <v>122894536.7381861</v>
       </c>
       <c r="D33">
-        <v>183267643.12766266</v>
-      </c>
-      <c r="F33">
-        <v>-487125253.5889262</v>
+        <v>30557980.738186106</v>
+      </c>
+      <c r="E33">
+        <v>196120938.70476145</v>
       </c>
       <c r="H33">
-        <v>-333347.5478546446</v>
+        <v>-521289303.28473747</v>
+      </c>
+      <c r="J33">
+        <v>-356726.54967599834</v>
       </c>
     </row>
     <row r="34"/>
@@ -2920,8 +3473,8 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="F35">
-        <v>7039318.370127523</v>
+      <c r="H35">
+        <v>7533014.028174066</v>
       </c>
     </row>
     <row r="36">
@@ -2929,19 +3482,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-1318325.079866358</v>
+        <v>-1529193.23425454</v>
       </c>
       <c r="C36">
-        <v>-1110690.079866358</v>
+        <v>-1410786.23425454</v>
       </c>
       <c r="D36">
-        <v>95200.81210175692</v>
-      </c>
-      <c r="F36">
-        <v>-404924.4995631597</v>
+        <v>-1188587.23425454</v>
+      </c>
+      <c r="E36">
+        <v>101877.62725712685</v>
       </c>
       <c r="H36">
-        <v>-319717.7204449795</v>
+        <v>-433323.4803677997</v>
+      </c>
+      <c r="J36">
+        <v>-342140.8077504291</v>
       </c>
     </row>
     <row r="37">
@@ -2949,19 +3505,22 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-45284930.19300657</v>
+        <v>-76243523.67072204</v>
       </c>
       <c r="C37">
-        <v>-47917312.19300657</v>
+        <v>-48460926.67072203</v>
       </c>
       <c r="D37">
-        <v>-57101108.82889805</v>
-      </c>
-      <c r="F37">
-        <v>-8221064.902076628</v>
+        <v>-51277945.67072203</v>
+      </c>
+      <c r="E37">
+        <v>-61105838.83487438</v>
       </c>
       <c r="H37">
-        <v>264214251.6545063</v>
+        <v>-8797641.188766234</v>
+      </c>
+      <c r="J37">
+        <v>282744657.8639193</v>
       </c>
     </row>
     <row r="38">
@@ -2969,19 +3528,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>68236521.75551173</v>
+        <v>35153373.83320954</v>
       </c>
       <c r="C38">
-        <v>-20472718.24448827</v>
+        <v>73022823.83320954</v>
       </c>
       <c r="D38">
-        <v>131358697.43460052</v>
-      </c>
-      <c r="F38">
-        <v>-488711924.62043846</v>
+        <v>-21908552.166790463</v>
+      </c>
+      <c r="E38">
+        <v>140571410.25141507</v>
       </c>
       <c r="H38">
-        <v>263561186.38620666</v>
+        <v>-522987253.9256974</v>
+      </c>
+      <c r="J38">
+        <v>282045790.50649285</v>
       </c>
     </row>
     <row r="39"/>
@@ -2990,27 +3552,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-52193857.23395288</v>
+        <v>-61043299.35781063</v>
       </c>
       <c r="C40">
-        <v>-121776846.23395288</v>
+        <v>-55853951.35781063</v>
       </c>
       <c r="D40">
-        <v>-249417127.3547229</v>
-      </c>
-      <c r="F40">
-        <v>383512914.43767697</v>
+        <v>-130317545.35781063</v>
+      </c>
+      <c r="E40">
+        <v>-266909751.83098128</v>
       </c>
       <c r="H40">
-        <v>-7232285.078110459</v>
+        <v>410410214.816382</v>
+      </c>
+      <c r="J40">
+        <v>-7739514.266091234</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>-862330.3848064956</v>
+      </c>
       <c r="C41">
-        <v>-2675888.5760770887</v>
+        <v>-2863559.3848064956</v>
+      </c>
+      <c r="D41">
+        <v>-2863559.3848064956</v>
       </c>
     </row>
     <row r="42">
@@ -3018,19 +3589,22 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-49517968.65787579</v>
+        <v>-60180968.97300415</v>
       </c>
       <c r="C42">
-        <v>-119100957.65787579</v>
+        <v>-52990391.97300415</v>
       </c>
       <c r="D42">
-        <v>-247113053.77981544</v>
-      </c>
-      <c r="F42">
-        <v>383512914.43767697</v>
+        <v>-127453985.97300415</v>
+      </c>
+      <c r="E42">
+        <v>-264444084.32610208</v>
       </c>
       <c r="H42">
-        <v>-7232285.078110459</v>
+        <v>410410214.816382</v>
+      </c>
+      <c r="J42">
+        <v>-7739514.266091234</v>
       </c>
     </row>
     <row r="43">
@@ -3038,19 +3612,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>16042664.521558851</v>
+        <v>-25889925.524601102</v>
       </c>
       <c r="C43">
-        <v>-142249564.47844115</v>
+        <v>17168872.475398898</v>
       </c>
       <c r="D43">
-        <v>-118058429.92012227</v>
-      </c>
-      <c r="F43">
-        <v>-105199010.18276146</v>
+        <v>-152226097.5246011</v>
+      </c>
+      <c r="E43">
+        <v>-126338341.57956615</v>
       </c>
       <c r="H43">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="J43">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="44">
@@ -3064,19 +3641,22 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>16042664.521558851</v>
+        <v>-25889925.524601102</v>
       </c>
       <c r="C46">
-        <v>-142249564.47844115</v>
+        <v>17168872.475398898</v>
       </c>
       <c r="D46">
-        <v>-118058429.92012227</v>
-      </c>
-      <c r="F46">
-        <v>-105199010.18276146</v>
+        <v>-152226097.5246011</v>
+      </c>
+      <c r="E46">
+        <v>-126338341.57956615</v>
       </c>
       <c r="H46">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="J46">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="47">
@@ -3089,19 +3669,22 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>16042664.521558851</v>
+        <v>-25889925.524601102</v>
       </c>
       <c r="C48">
-        <v>-142249564.47844115</v>
+        <v>17168872.475398898</v>
       </c>
       <c r="D48">
-        <v>-118058429.92012227</v>
-      </c>
-      <c r="F48">
-        <v>-105199010.18276146</v>
+        <v>-152226097.5246011</v>
+      </c>
+      <c r="E48">
+        <v>-126338341.57956615</v>
       </c>
       <c r="H48">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="J48">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="49"/>
@@ -3110,31 +3693,34 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>397340.6823303082</v>
+        <v>459052.18277284026</v>
       </c>
       <c r="C50">
-        <v>391842.6823303082</v>
+        <v>425207.7795856593</v>
       </c>
       <c r="D50">
-        <v>401140.14816142886</v>
-      </c>
-      <c r="F50">
-        <v>192065.4623307066</v>
+        <v>419324.18277284026</v>
+      </c>
+      <c r="E50">
+        <v>429273.71720923093</v>
       </c>
       <c r="H50">
-        <v>5287.527910821971</v>
+        <v>205535.78428911715</v>
+      </c>
+      <c r="J50">
+        <v>5658.363471044746</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:J129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3144,6 +3730,8 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3151,24 +3739,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -3182,25 +3776,31 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-66606177</v>
+        <v>-214683652</v>
       </c>
       <c r="C3">
-        <v>-134290376.9134487</v>
+        <v>-71277535.59681024</v>
       </c>
       <c r="D3">
-        <v>-39904554.98259754</v>
+        <v>-143708700.18192762</v>
       </c>
       <c r="E3">
-        <v>76024005</v>
+        <v>-42703221.628332876</v>
       </c>
       <c r="F3">
-        <v>205770169.05862767</v>
+        <v>10953760</v>
       </c>
       <c r="G3">
-        <v>-28443973.037591033</v>
+        <v>81355873.68420169</v>
       </c>
       <c r="H3">
-        <v>2555030.3236488546</v>
+        <v>220201657.1201496</v>
+      </c>
+      <c r="I3">
+        <v>-30438863.06072792</v>
+      </c>
+      <c r="J3">
+        <v>2734224.8579258774</v>
       </c>
     </row>
     <row r="4">
@@ -3208,25 +3808,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>56068529</v>
+        <v>47107836</v>
       </c>
       <c r="C4">
-        <v>-142249564.47844115</v>
+        <v>60000840.037077755</v>
       </c>
       <c r="D4">
-        <v>-111691385.78545593</v>
+        <v>-152226097.5246011</v>
       </c>
       <c r="E4">
-        <v>-102223700</v>
+        <v>-119524751.07796535</v>
       </c>
       <c r="F4">
-        <v>-105199010.18276146</v>
+        <v>-79228336</v>
       </c>
       <c r="G4">
-        <v>-98831966.04809512</v>
+        <v>-109393058.47845991</v>
       </c>
       <c r="H4">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="I4">
+        <v>-105763448.6077146</v>
+      </c>
+      <c r="J4">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="5">
@@ -3234,25 +3840,31 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-40155854</v>
+        <v>23580508</v>
       </c>
       <c r="C5">
-        <v>290626059.90160704</v>
+        <v>-42972145.25471587</v>
       </c>
       <c r="D5">
-        <v>235914009.14148217</v>
+        <v>311008832.25886846</v>
       </c>
       <c r="E5">
-        <v>153197014</v>
+        <v>252459605.72648108</v>
       </c>
       <c r="F5">
-        <v>165014953.72463977</v>
+        <v>191456114</v>
       </c>
       <c r="G5">
-        <v>141050496.20313215</v>
+        <v>163941335.6318294</v>
       </c>
       <c r="H5">
-        <v>-22357843.54133192</v>
+        <v>176588114.9148375</v>
+      </c>
+      <c r="I5">
+        <v>150942933.7772456</v>
+      </c>
+      <c r="J5">
+        <v>-23925888.868913762</v>
       </c>
     </row>
     <row r="6">
@@ -3260,25 +3872,31 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>99955</v>
+        <v>243988</v>
       </c>
       <c r="C6">
-        <v>391842.6823303082</v>
+        <v>106965.24543931065</v>
       </c>
       <c r="D6">
-        <v>289858.8687629309</v>
+        <v>419324.18277284026</v>
       </c>
       <c r="E6">
-        <v>94457</v>
+        <v>310187.8349255949</v>
       </c>
       <c r="F6">
-        <v>192065.4623307066</v>
+        <v>204260</v>
       </c>
       <c r="G6">
-        <v>80784.18293220864</v>
+        <v>101081.64862649159</v>
       </c>
       <c r="H6">
-        <v>5287.527910821971</v>
+        <v>205535.78428911715</v>
+      </c>
+      <c r="I6">
+        <v>86449.90200548114</v>
+      </c>
+      <c r="J6">
+        <v>5658.363471044746</v>
       </c>
     </row>
     <row r="7">
@@ -3291,7 +3909,13 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1276289</v>
+        <v>1504283</v>
+      </c>
+      <c r="C8">
+        <v>1365800.2714870926</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3314,19 +3938,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>4139558</v>
+        <v>9215148</v>
       </c>
       <c r="C12">
-        <v>-4944210.53926867</v>
+        <v>4429881.821622349</v>
       </c>
       <c r="D12">
-        <v>-5967440.175675252</v>
+        <v>-5290967.873908256</v>
       </c>
       <c r="E12">
-        <v>333392</v>
+        <v>-6385960.712675768</v>
+      </c>
+      <c r="F12">
+        <v>-536123</v>
       </c>
       <c r="G12">
-        <v>-30454.180006659324</v>
+        <v>356774.1194287695</v>
+      </c>
+      <c r="I12">
+        <v>-32590.05391491433</v>
       </c>
     </row>
     <row r="13">
@@ -3358,23 +3988,29 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>119013603.95535406</v>
+      <c r="B18">
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>90550004.89064763</v>
+        <v>127360505.80462569</v>
       </c>
       <c r="E18">
-        <v>95322966</v>
+        <v>96900640.26470816</v>
       </c>
       <c r="F18">
-        <v>549479710.119606</v>
+        <v>74718475</v>
       </c>
       <c r="G18">
-        <v>672724998.0409008</v>
+        <v>102008348.29866505</v>
       </c>
       <c r="H18">
-        <v>18703942.77096762</v>
+        <v>588016928.1863331</v>
+      </c>
+      <c r="I18">
+        <v>719905902.9423714</v>
+      </c>
+      <c r="J18">
+        <v>20015725.36820941</v>
       </c>
     </row>
     <row r="19">
@@ -3387,45 +4023,51 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>-33786197</v>
+        <v>11961330</v>
       </c>
       <c r="C20">
-        <v>121776846.23395288</v>
+        <v>-36155758.63704568</v>
       </c>
       <c r="D20">
-        <v>103991104.41803482</v>
+        <v>130317545.35781063</v>
       </c>
       <c r="E20">
-        <v>35796792</v>
+        <v>111284418.06392953</v>
       </c>
       <c r="F20">
-        <v>-383512914.43767697</v>
+        <v>81235576</v>
       </c>
       <c r="G20">
-        <v>-528938937.37436503</v>
+        <v>38307364.73633087</v>
       </c>
       <c r="H20">
-        <v>7232285.078110459</v>
+        <v>-410410214.816382</v>
+      </c>
+      <c r="I20">
+        <v>-566035548.5834337</v>
+      </c>
+      <c r="J20">
+        <v>7739514.266091234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>54387977.56923848</v>
-      </c>
       <c r="D21">
-        <v>47050482.2401341</v>
-      </c>
-      <c r="F21">
-        <v>-1143906.3191979213</v>
-      </c>
-      <c r="G21">
-        <v>-2785894.466329147</v>
+        <v>58202424.78756756</v>
+      </c>
+      <c r="E21">
+        <v>50350321.453192644</v>
       </c>
       <c r="H21">
-        <v>48299357.81789879</v>
+        <v>-1224133.0618036524</v>
+      </c>
+      <c r="I21">
+        <v>-2981280.429782548</v>
+      </c>
+      <c r="J21">
+        <v>51686785.6890864</v>
       </c>
     </row>
     <row r="22">
@@ -3463,25 +4105,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-82518852</v>
+        <v>-277032846</v>
       </c>
       <c r="C28">
-        <v>-282666872.3366146</v>
+        <v>-88306230.37917213</v>
       </c>
       <c r="D28">
-        <v>-164127179.43904585</v>
+        <v>-302491434.916195</v>
       </c>
       <c r="E28">
-        <v>25050691</v>
+        <v>-175638077.4544477</v>
       </c>
       <c r="F28">
-        <v>145954224.4163273</v>
+        <v>-101274018</v>
       </c>
       <c r="G28">
-        <v>-70662503.19262807</v>
+        <v>26807596.53083218</v>
       </c>
       <c r="H28">
-        <v>-231416027.4431154</v>
+        <v>156190580.13702843</v>
+      </c>
+      <c r="I28">
+        <v>-75618348.23025896</v>
+      </c>
+      <c r="J28">
+        <v>-247646162.513562</v>
       </c>
     </row>
     <row r="29">
@@ -3499,25 +4147,31 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-10459840</v>
+        <v>-3551443</v>
       </c>
       <c r="C31">
-        <v>-18337730.018412746</v>
+        <v>-11193430.572316734</v>
       </c>
       <c r="D31">
-        <v>-16793952.337667584</v>
+        <v>-19623828.64508363</v>
       </c>
       <c r="E31">
-        <v>-16211616</v>
+        <v>-17971779.63778398</v>
       </c>
       <c r="F31">
-        <v>718709.8447808257</v>
+        <v>-17379275</v>
       </c>
       <c r="G31">
-        <v>-362010.24077726266</v>
+        <v>-17348601.71485024</v>
       </c>
       <c r="H31">
-        <v>-3615244.0444581048</v>
+        <v>769115.8515995186</v>
+      </c>
+      <c r="I31">
+        <v>-387399.47232538485</v>
+      </c>
+      <c r="J31">
+        <v>-3868795.6234152094</v>
       </c>
     </row>
     <row r="32">
@@ -3530,25 +4184,31 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-170801</v>
+        <v>-197421</v>
       </c>
       <c r="C33">
-        <v>-73346.43035172047</v>
+        <v>-182779.9598447271</v>
       </c>
       <c r="D33">
-        <v>-4118.879702436345</v>
+        <v>-78490.50997618012</v>
       </c>
       <c r="E33">
-        <v>4627</v>
+        <v>-4407.753272033399</v>
       </c>
       <c r="F33">
-        <v>186710.80867533517</v>
+        <v>-385957</v>
       </c>
       <c r="G33">
-        <v>-264366.4917427224</v>
+        <v>4951.510086015611</v>
       </c>
       <c r="H33">
-        <v>-442158.3797693142</v>
+        <v>199805.587275568</v>
+      </c>
+      <c r="I33">
+        <v>-282907.57516072027</v>
+      </c>
+      <c r="J33">
+        <v>-473168.72207566025</v>
       </c>
     </row>
     <row r="34">
@@ -3571,25 +4231,31 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-43471430</v>
+        <v>-118401221</v>
       </c>
       <c r="C37">
-        <v>-258775787.6555877</v>
+        <v>-46520255.91063791</v>
       </c>
       <c r="D37">
-        <v>-177402710.5664467</v>
+        <v>-276924772.55095667</v>
       </c>
       <c r="E37">
-        <v>-33405896</v>
+        <v>-189844674.87708429</v>
       </c>
       <c r="F37">
-        <v>-117101245.41382009</v>
+        <v>-96809213</v>
       </c>
       <c r="G37">
-        <v>-64916433.81867855</v>
+        <v>-35748785.601121366</v>
       </c>
       <c r="H37">
-        <v>-223083966.27094913</v>
+        <v>-125314025.88102862</v>
+      </c>
+      <c r="I37">
+        <v>-69469283.94237123</v>
+      </c>
+      <c r="J37">
+        <v>-238729740.44066802</v>
       </c>
     </row>
     <row r="38">
@@ -3602,25 +4268,31 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-54657957</v>
+        <v>-164001313</v>
       </c>
       <c r="C39">
-        <v>-216280507.95957163</v>
+        <v>-58491338.959694736</v>
       </c>
       <c r="D39">
-        <v>-146225777.76442498</v>
+        <v>-231449128.28407142</v>
       </c>
       <c r="E39">
-        <v>-43259390</v>
+        <v>-156481178.61163336</v>
       </c>
       <c r="F39">
-        <v>-121849759.09802014</v>
+        <v>-109354509</v>
       </c>
       <c r="G39">
-        <v>-71982802.76343746</v>
+        <v>-46293344.694160976</v>
       </c>
       <c r="H39">
-        <v>-5731148.75148483</v>
+        <v>-130395571.8937582</v>
+      </c>
+      <c r="I39">
+        <v>-77031245.71057554</v>
+      </c>
+      <c r="J39">
+        <v>-6133097.222267757</v>
       </c>
     </row>
     <row r="40">
@@ -3628,25 +4300,31 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-17424544</v>
+        <v>-1686030</v>
       </c>
       <c r="C40">
-        <v>43059240.49032548</v>
+        <v>-18646597.225031942</v>
       </c>
       <c r="D40">
-        <v>42921694.33763344</v>
+        <v>46079157.89583281</v>
       </c>
       <c r="E40">
-        <v>5443214</v>
+        <v>45931965.07924597</v>
       </c>
       <c r="F40">
-        <v>2420125.183857115</v>
+        <v>16469849</v>
       </c>
       <c r="G40">
-        <v>13717481.527404258</v>
+        <v>5824968.450689729</v>
       </c>
       <c r="H40">
-        <v>362195.11168028414</v>
+        <v>2589858.2790769157</v>
+      </c>
+      <c r="I40">
+        <v>14679543.578490384</v>
+      </c>
+      <c r="J40">
+        <v>387597.3089670364</v>
       </c>
     </row>
     <row r="41">
@@ -3659,13 +4337,19 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>343622</v>
+        <v>1413273</v>
       </c>
       <c r="C42">
-        <v>293083.1053453884</v>
-      </c>
-      <c r="E42">
-        <v>-150091</v>
+        <v>367721.59039914765</v>
+      </c>
+      <c r="D42">
+        <v>313638.20016392187</v>
+      </c>
+      <c r="F42">
+        <v>435743</v>
+      </c>
+      <c r="G42">
+        <v>-160617.48440029589</v>
       </c>
     </row>
     <row r="43">
@@ -3678,25 +4362,31 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-56164</v>
+        <v>-891168</v>
       </c>
       <c r="C44">
-        <v>-100663914.5501911</v>
+        <v>-60103.00680159515</v>
       </c>
       <c r="D44">
-        <v>-100731095.31584264</v>
+        <v>-107723879.0129857</v>
       </c>
       <c r="E44">
-        <v>-100305626</v>
+        <v>-107795771.43544298</v>
       </c>
       <c r="F44">
-        <v>82122883.76040092</v>
+        <v>-107887174</v>
       </c>
       <c r="G44">
-        <v>-17732164.46754718</v>
+        <v>-107340462.24834876</v>
       </c>
       <c r="H44">
-        <v>721869.1564628173</v>
+        <v>87882491.29723638</v>
+      </c>
+      <c r="I44">
+        <v>-18975792.350972008</v>
+      </c>
+      <c r="J44">
+        <v>772496.738493456</v>
       </c>
     </row>
     <row r="45">
@@ -3714,33 +4404,45 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>43378262</v>
+        <v>17733049</v>
       </c>
       <c r="C47">
-        <v>298851880.8277483</v>
+        <v>46420553.664756365</v>
       </c>
       <c r="D47">
-        <v>252932883.34280437</v>
+        <v>319811563.03076094</v>
       </c>
       <c r="E47">
-        <v>211139793</v>
+        <v>270672081.9012115</v>
       </c>
       <c r="F47">
-        <v>310851482.50148696</v>
+        <v>218405271</v>
       </c>
       <c r="G47">
-        <v>76103129.52085876</v>
+        <v>225947874.3459581</v>
+      </c>
+      <c r="H47">
+        <v>332652744.9446764</v>
+      </c>
+      <c r="I47">
+        <v>81440547.52536947</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C48">
-        <v>-31400043.37099551</v>
-      </c>
-      <c r="E48">
-        <v>1795676</v>
+      <c r="B48">
+        <v>-7450572</v>
+      </c>
+      <c r="D48">
+        <v>-33602254.4743488</v>
+      </c>
+      <c r="F48">
+        <v>-4768753</v>
+      </c>
+      <c r="G48">
+        <v>1921613.966979937</v>
       </c>
     </row>
     <row r="49">
@@ -3748,16 +4450,28 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-66606177</v>
-      </c>
-      <c r="E49">
-        <v>76024005</v>
+        <v>-206344502</v>
+      </c>
+      <c r="C49">
+        <v>-71277535.59681024</v>
+      </c>
+      <c r="F49">
+        <v>10953760</v>
+      </c>
+      <c r="G49">
+        <v>81355873.68420169</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
+      <c r="B50">
+        <v>-8339150</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -3818,17 +4532,17 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="D62">
-        <v>407731.67619177717</v>
-      </c>
-      <c r="F62">
-        <v>707428.3180083497</v>
-      </c>
-      <c r="G62">
-        <v>704161.1649662623</v>
+      <c r="E62">
+        <v>436327.5355633533</v>
       </c>
       <c r="H62">
-        <v>372423.53455876285</v>
+        <v>757043.1060625465</v>
+      </c>
+      <c r="I62">
+        <v>753546.8144609791</v>
+      </c>
+      <c r="J62">
+        <v>398543.09220602934</v>
       </c>
     </row>
     <row r="63">
@@ -3852,25 +4566,31 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-691414</v>
+      </c>
+      <c r="C67">
         <v>0</v>
       </c>
-      <c r="C67">
-        <v>618231.4085666231</v>
-      </c>
       <c r="D67">
-        <v>575388.6772134427</v>
+        <v>661590.4592628641</v>
       </c>
       <c r="E67">
-        <v>484092</v>
+        <v>615742.9951591835</v>
       </c>
       <c r="F67">
-        <v>-3491507.087968536</v>
+        <v>554413</v>
       </c>
       <c r="G67">
-        <v>-3480345.507198616</v>
+        <v>518043.3154440175</v>
       </c>
       <c r="H67">
-        <v>-117509.66815505411</v>
+        <v>-3736380.497400303</v>
+      </c>
+      <c r="I67">
+        <v>-3724436.110160593</v>
+      </c>
+      <c r="J67">
+        <v>-125751.09294880005</v>
       </c>
     </row>
     <row r="68">
@@ -3922,34 +4642,46 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>484100.96589230676</v>
+      <c r="B77">
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>-91265.70288030007</v>
+        <v>518052.9101503471</v>
       </c>
       <c r="E77">
-        <v>484092</v>
+        <v>-97666.53302768744</v>
       </c>
       <c r="F77">
-        <v>-3491507.087968536</v>
+        <v>554413</v>
       </c>
       <c r="G77">
-        <v>-3480345.507198616</v>
+        <v>518043.3154440175</v>
       </c>
       <c r="H77">
-        <v>-117509.66815505411</v>
+        <v>-3736380.497400303</v>
+      </c>
+      <c r="I77">
+        <v>-3724436.110160593</v>
+      </c>
+      <c r="J77">
+        <v>-125751.09294880005</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="C78">
-        <v>-134130.44267431635</v>
+      <c r="B78">
+        <v>-691414</v>
       </c>
       <c r="D78">
-        <v>484122.9743331427</v>
+        <v>-143537.54911251698</v>
+      </c>
+      <c r="E78">
+        <v>518076.46213149617</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4063,25 +4795,31 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>720222009</v>
+        <v>769738313</v>
       </c>
       <c r="C101">
-        <v>2017125.3224450534</v>
+        <v>770734069.9662689</v>
       </c>
       <c r="D101">
-        <v>1887227.1029434784</v>
+        <v>2158594.419460595</v>
       </c>
       <c r="E101">
-        <v>2441315</v>
+        <v>2019585.9163230287</v>
       </c>
       <c r="F101">
-        <v>32653001.514535256</v>
+        <v>3907358</v>
       </c>
       <c r="G101">
-        <v>33182283.608619556</v>
+        <v>2612534.2220966504</v>
       </c>
       <c r="H101">
-        <v>101934.29457549653</v>
+        <v>34943087.6027457</v>
+      </c>
+      <c r="I101">
+        <v>35509490.3749968</v>
+      </c>
+      <c r="J101">
+        <v>109083.35588966013</v>
       </c>
     </row>
     <row r="102">
@@ -4098,6 +4836,12 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B104">
+        <v>770407137</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4123,23 +4867,29 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C109">
-        <v>2789484.04302948</v>
+      <c r="B109">
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>2627459.0020177183</v>
+        <v>2985121.757907948</v>
       </c>
       <c r="E109">
-        <v>1528090</v>
+        <v>2811733.250288144</v>
       </c>
       <c r="F109">
-        <v>405501.12071305997</v>
+        <v>2930079</v>
       </c>
       <c r="G109">
-        <v>21498.9454305367</v>
+        <v>1635261.0865224972</v>
       </c>
       <c r="H109">
-        <v>101934.29457549653</v>
+        <v>433940.5422739032</v>
+      </c>
+      <c r="I109">
+        <v>23006.75278539047</v>
+      </c>
+      <c r="J109">
+        <v>109083.35588966013</v>
       </c>
     </row>
     <row r="110">
@@ -4147,7 +4897,13 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-73856</v>
+        <v>-1084934</v>
+      </c>
+      <c r="C110">
+        <v>-79035.81778966261</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4215,22 +4971,28 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>720295865</v>
+        <v>416110</v>
       </c>
       <c r="C123">
-        <v>-772358.7205844269</v>
+        <v>770813105.7840586</v>
       </c>
       <c r="D123">
-        <v>-740231.8990742401</v>
+        <v>-826527.3384473531</v>
       </c>
       <c r="E123">
-        <v>913225</v>
+        <v>-792147.3339651155</v>
       </c>
       <c r="F123">
-        <v>32247500.393822197</v>
+        <v>977279</v>
       </c>
       <c r="G123">
-        <v>33160783.562766977</v>
+        <v>977273.135574153</v>
+      </c>
+      <c r="H123">
+        <v>34509147.060471795</v>
+      </c>
+      <c r="I123">
+        <v>35486482.444612354</v>
       </c>
     </row>
     <row r="124">
@@ -4243,25 +5005,31 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>653615832</v>
+        <v>554363247</v>
       </c>
       <c r="C125">
-        <v>-131655020.18243703</v>
+        <v>699456534.3694586</v>
       </c>
       <c r="D125">
-        <v>-37441939.20244061</v>
+        <v>-140888515.30320418</v>
       </c>
       <c r="E125">
-        <v>78949412</v>
+        <v>-40067892.71685065</v>
       </c>
       <c r="F125">
-        <v>234931662.38477233</v>
+        <v>15415531</v>
       </c>
       <c r="G125">
-        <v>1257965.0638299084</v>
+        <v>84486451.22174236</v>
       </c>
       <c r="H125">
-        <v>2539454.9500692966</v>
+        <v>251408363.04789594</v>
+      </c>
+      <c r="I125">
+        <v>1346191.204108291</v>
+      </c>
+      <c r="J125">
+        <v>2717557.120866737</v>
       </c>
     </row>
     <row r="126">
@@ -4269,10 +5037,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>4441269</v>
-      </c>
-      <c r="E126">
-        <v>-21689534</v>
+        <v>-7855462</v>
+      </c>
+      <c r="C126">
+        <v>4752753.025331417</v>
+      </c>
+      <c r="F126">
+        <v>-36280922</v>
+      </c>
+      <c r="G126">
+        <v>-23210708.096386105</v>
       </c>
     </row>
     <row r="127">
@@ -4280,25 +5054,31 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>658057101</v>
+        <v>546507785</v>
       </c>
       <c r="C127">
-        <v>-187645957.23025042</v>
+        <v>704209287.39479</v>
       </c>
       <c r="D127">
-        <v>-85541430.66615441</v>
+        <v>-200806321.5529801</v>
       </c>
       <c r="E127">
-        <v>57259878</v>
+        <v>-91540794.62192969</v>
       </c>
       <c r="F127">
-        <v>233794496.1505804</v>
+        <v>-20865391</v>
       </c>
       <c r="G127">
-        <v>-724688.4377338946</v>
+        <v>61275743.12535625</v>
       </c>
       <c r="H127">
-        <v>2539454.9500692966</v>
+        <v>250191442.78031915</v>
+      </c>
+      <c r="I127">
+        <v>-775513.7472786417</v>
+      </c>
+      <c r="J127">
+        <v>2717557.120866737</v>
       </c>
     </row>
     <row r="128">
@@ -4306,10 +5086,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>48676278</v>
-      </c>
-      <c r="E128">
-        <v>236318764</v>
+        <v>52090470</v>
+      </c>
+      <c r="C128">
+        <v>52090140.79677972</v>
+      </c>
+      <c r="F128">
+        <v>252894345</v>
+      </c>
+      <c r="G128">
+        <v>252892747.668196</v>
       </c>
     </row>
     <row r="129">
@@ -4317,22 +5103,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>706733379</v>
-      </c>
-      <c r="E129">
-        <v>293578642</v>
+        <v>598598255</v>
+      </c>
+      <c r="C129">
+        <v>756299428.1915698</v>
+      </c>
+      <c r="F129">
+        <v>232028954</v>
+      </c>
+      <c r="G129">
+        <v>314168490.7935522</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:J129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4342,6 +5134,8 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4349,24 +5143,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -4380,16 +5180,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-66606177</v>
+        <v>-143406116.40318978</v>
       </c>
       <c r="C3">
-        <v>-94385821.93085116</v>
+        <v>-71277535.59681024</v>
+      </c>
+      <c r="D3">
+        <v>-101005478.55359474</v>
       </c>
       <c r="E3">
-        <v>76024005</v>
+        <v>-53656981.628332876</v>
       </c>
       <c r="F3">
-        <v>234214142.0962187</v>
+        <v>-70402113.68420169</v>
+      </c>
+      <c r="G3">
+        <v>81355873.68420169</v>
+      </c>
+      <c r="H3">
+        <v>250640520.18087754</v>
       </c>
     </row>
     <row r="4">
@@ -4397,16 +5206,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>56068529</v>
+        <v>-12893004.037077755</v>
       </c>
       <c r="C4">
-        <v>-30558178.69298522</v>
+        <v>60000840.037077755</v>
+      </c>
+      <c r="D4">
+        <v>-32701346.446635753</v>
       </c>
       <c r="E4">
-        <v>-102223700</v>
+        <v>-40296415.07796535</v>
       </c>
       <c r="F4">
-        <v>-6367044.134666339</v>
+        <v>30164722.47845991</v>
+      </c>
+      <c r="G4">
+        <v>-109393058.47845991</v>
+      </c>
+      <c r="H4">
+        <v>-6813590.501600802</v>
       </c>
     </row>
     <row r="5">
@@ -4414,16 +5232,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-40155854</v>
+        <v>66552653.25471587</v>
       </c>
       <c r="C5">
-        <v>54712050.76012486</v>
+        <v>-42972145.25471587</v>
+      </c>
+      <c r="D5">
+        <v>58549226.532387376</v>
       </c>
       <c r="E5">
-        <v>153197014</v>
+        <v>61003491.72648108</v>
       </c>
       <c r="F5">
-        <v>23964457.52150762</v>
+        <v>27514778.36817059</v>
+      </c>
+      <c r="G5">
+        <v>163941335.6318294</v>
+      </c>
+      <c r="H5">
+        <v>25645181.1375919</v>
       </c>
     </row>
     <row r="6">
@@ -4431,16 +5258,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>99955</v>
+        <v>137022.75456068935</v>
       </c>
       <c r="C6">
-        <v>101983.81356737728</v>
+        <v>106965.24543931065</v>
+      </c>
+      <c r="D6">
+        <v>109136.34784724534</v>
       </c>
       <c r="E6">
-        <v>94457</v>
+        <v>105927.83492559491</v>
       </c>
       <c r="F6">
-        <v>111281.27939849795</v>
+        <v>103178.35137350841</v>
+      </c>
+      <c r="G6">
+        <v>101081.64862649159</v>
+      </c>
+      <c r="H6">
+        <v>119085.882283636</v>
       </c>
     </row>
     <row r="7">
@@ -4453,7 +5289,10 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1276289</v>
+        <v>138482.7285129074</v>
+      </c>
+      <c r="C8">
+        <v>1365800.2714870926</v>
       </c>
     </row>
     <row r="9">
@@ -4476,13 +5315,22 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>4139558</v>
+        <v>4785266.178377651</v>
       </c>
       <c r="C12">
-        <v>1023229.6364065828</v>
+        <v>4429881.821622349</v>
+      </c>
+      <c r="D12">
+        <v>1094992.8387675118</v>
       </c>
       <c r="E12">
-        <v>333392</v>
+        <v>-5849837.712675768</v>
+      </c>
+      <c r="F12">
+        <v>-892897.1194287695</v>
+      </c>
+      <c r="G12">
+        <v>356774.1194287695</v>
       </c>
     </row>
     <row r="13">
@@ -4514,14 +5362,20 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>28463599.06470643</v>
+      <c r="D18">
+        <v>30459865.53991753</v>
       </c>
       <c r="E18">
-        <v>95322966</v>
+        <v>22182165.26470816</v>
       </c>
       <c r="F18">
-        <v>-123245287.92129481</v>
+        <v>-27289873.298665047</v>
+      </c>
+      <c r="G18">
+        <v>102008348.29866505</v>
+      </c>
+      <c r="H18">
+        <v>-131888974.75603831</v>
       </c>
     </row>
     <row r="19">
@@ -4534,27 +5388,36 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>-33786197</v>
+        <v>48117088.63704568</v>
       </c>
       <c r="C20">
-        <v>17785741.81591806</v>
+        <v>-36155758.63704568</v>
+      </c>
+      <c r="D20">
+        <v>19033127.293881103</v>
       </c>
       <c r="E20">
-        <v>35796792</v>
+        <v>30048842.063929528</v>
       </c>
       <c r="F20">
-        <v>145426022.93668807</v>
+        <v>42928211.26366913</v>
+      </c>
+      <c r="G20">
+        <v>38307364.73633087</v>
+      </c>
+      <c r="H20">
+        <v>155625333.76705176</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>7337495.329104379</v>
-      </c>
-      <c r="F21">
-        <v>1641988.1471312258</v>
+      <c r="D21">
+        <v>7852103.3343749195</v>
+      </c>
+      <c r="H21">
+        <v>1757147.3679788955</v>
       </c>
     </row>
     <row r="22">
@@ -4592,16 +5455,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-82518852</v>
+        <v>-188726615.62082785</v>
       </c>
       <c r="C28">
-        <v>-118539692.89756876</v>
+        <v>-88306230.37917213</v>
+      </c>
+      <c r="D28">
+        <v>-126853357.46174729</v>
       </c>
       <c r="E28">
-        <v>25050691</v>
+        <v>-74364059.45444769</v>
       </c>
       <c r="F28">
-        <v>216616727.60895538</v>
+        <v>-128081614.53083217</v>
+      </c>
+      <c r="G28">
+        <v>26807596.53083218</v>
+      </c>
+      <c r="H28">
+        <v>231808928.3672874</v>
       </c>
     </row>
     <row r="29">
@@ -4619,16 +5491,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-10459840</v>
+        <v>7641987.572316734</v>
       </c>
       <c r="C31">
-        <v>-1543777.680745162</v>
+        <v>-11193430.572316734</v>
+      </c>
+      <c r="D31">
+        <v>-1652049.0072996467</v>
       </c>
       <c r="E31">
-        <v>-16211616</v>
+        <v>-592504.6377839819</v>
       </c>
       <c r="F31">
-        <v>1080720.0855580883</v>
+        <v>-30673.285149760544</v>
+      </c>
+      <c r="G31">
+        <v>-17348601.71485024</v>
+      </c>
+      <c r="H31">
+        <v>1156515.3239249033</v>
       </c>
     </row>
     <row r="32">
@@ -4641,16 +5522,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-170801</v>
+        <v>-14641.040155272902</v>
       </c>
       <c r="C33">
-        <v>-69227.55064928412</v>
+        <v>-182779.9598447271</v>
+      </c>
+      <c r="D33">
+        <v>-74082.75670414673</v>
       </c>
       <c r="E33">
-        <v>4627</v>
+        <v>381549.2467279666</v>
       </c>
       <c r="F33">
-        <v>451077.3004180576</v>
+        <v>-390908.5100860156</v>
+      </c>
+      <c r="G33">
+        <v>4951.510086015611</v>
+      </c>
+      <c r="H33">
+        <v>482713.16243628826</v>
       </c>
     </row>
     <row r="34">
@@ -4673,16 +5563,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-43471430</v>
+        <v>-71880965.08936208</v>
       </c>
       <c r="C37">
-        <v>-81373077.08914101</v>
+        <v>-46520255.91063791</v>
+      </c>
+      <c r="D37">
+        <v>-87080097.67387238</v>
       </c>
       <c r="E37">
-        <v>-33405896</v>
+        <v>-93035461.87708429</v>
       </c>
       <c r="F37">
-        <v>-52184811.59514154</v>
+        <v>-61060427.398878634</v>
+      </c>
+      <c r="G37">
+        <v>-35748785.601121366</v>
+      </c>
+      <c r="H37">
+        <v>-55844741.93865739</v>
       </c>
     </row>
     <row r="38">
@@ -4695,16 +5594,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-54657957</v>
+        <v>-105509974.04030526</v>
       </c>
       <c r="C39">
-        <v>-70054730.19514665</v>
+        <v>-58491338.959694736</v>
+      </c>
+      <c r="D39">
+        <v>-74967949.67243806</v>
       </c>
       <c r="E39">
-        <v>-43259390</v>
+        <v>-47126669.61163336</v>
       </c>
       <c r="F39">
-        <v>-49866956.33458267</v>
+        <v>-63061164.305839024</v>
+      </c>
+      <c r="G39">
+        <v>-46293344.694160976</v>
+      </c>
+      <c r="H39">
+        <v>-53364326.18318266</v>
       </c>
     </row>
     <row r="40">
@@ -4712,16 +5620,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-17424544</v>
+        <v>16960567.225031942</v>
       </c>
       <c r="C40">
-        <v>137546.1526920423</v>
+        <v>-18646597.225031942</v>
+      </c>
+      <c r="D40">
+        <v>147192.81658683717</v>
       </c>
       <c r="E40">
-        <v>5443214</v>
+        <v>29462116.07924597</v>
       </c>
       <c r="F40">
-        <v>-11297356.343547143</v>
+        <v>10644880.54931027</v>
+      </c>
+      <c r="G40">
+        <v>5824968.450689729</v>
+      </c>
+      <c r="H40">
+        <v>-12089685.299413469</v>
       </c>
     </row>
     <row r="41">
@@ -4734,10 +5651,16 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>343622</v>
-      </c>
-      <c r="E42">
-        <v>-150091</v>
+        <v>1045551.4096008523</v>
+      </c>
+      <c r="C42">
+        <v>367721.59039914765</v>
+      </c>
+      <c r="F42">
+        <v>596360.4844002959</v>
+      </c>
+      <c r="G42">
+        <v>-160617.48440029589</v>
       </c>
     </row>
     <row r="43">
@@ -4750,16 +5673,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-56164</v>
+        <v>-831064.9931984049</v>
       </c>
       <c r="C44">
-        <v>67180.76565153897</v>
+        <v>-60103.00680159515</v>
+      </c>
+      <c r="D44">
+        <v>71892.42245727777</v>
       </c>
       <c r="E44">
-        <v>-100305626</v>
+        <v>91402.5645570159</v>
       </c>
       <c r="F44">
-        <v>99855048.2279481</v>
+        <v>-546711.7516512424</v>
+      </c>
+      <c r="G44">
+        <v>-107340462.24834876</v>
+      </c>
+      <c r="H44">
+        <v>106858283.6482084</v>
       </c>
     </row>
     <row r="45">
@@ -4777,24 +5709,36 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>43378262</v>
+        <v>-28687504.664756365</v>
       </c>
       <c r="C47">
-        <v>45918997.48494393</v>
+        <v>46420553.664756365</v>
+      </c>
+      <c r="D47">
+        <v>49139481.12954944</v>
       </c>
       <c r="E47">
-        <v>211139793</v>
+        <v>52266810.9012115</v>
       </c>
       <c r="F47">
-        <v>234748352.9806282</v>
+        <v>-7542603.345958114</v>
+      </c>
+      <c r="G47">
+        <v>225947874.3459581</v>
+      </c>
+      <c r="H47">
+        <v>251212197.41930693</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="E48">
-        <v>1795676</v>
+      <c r="F48">
+        <v>-6690366.966979937</v>
+      </c>
+      <c r="G48">
+        <v>1921613.966979937</v>
       </c>
     </row>
     <row r="49">
@@ -4802,10 +5746,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-66606177</v>
-      </c>
-      <c r="E49">
-        <v>76024005</v>
+        <v>-135066966.40318978</v>
+      </c>
+      <c r="C49">
+        <v>-71277535.59681024</v>
+      </c>
+      <c r="F49">
+        <v>-70402113.68420169</v>
+      </c>
+      <c r="G49">
+        <v>81355873.68420169</v>
       </c>
     </row>
     <row r="50">
@@ -4872,8 +5822,8 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="F62">
-        <v>3267.153042087448</v>
+      <c r="H62">
+        <v>3496.2916015674127</v>
       </c>
     </row>
     <row r="63">
@@ -4897,16 +5847,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-691414</v>
+      </c>
+      <c r="C67">
         <v>0</v>
       </c>
-      <c r="C67">
-        <v>42842.73135318037</v>
+      <c r="D67">
+        <v>45847.46410368057</v>
       </c>
       <c r="E67">
-        <v>484092</v>
+        <v>61329.99515918351</v>
       </c>
       <c r="F67">
-        <v>-11161.580769920256</v>
+        <v>36369.68455598247</v>
+      </c>
+      <c r="G67">
+        <v>518043.3154440175</v>
+      </c>
+      <c r="H67">
+        <v>-11944.387239709962</v>
       </c>
     </row>
     <row r="68">
@@ -4958,22 +5917,31 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>575366.6687726069</v>
+      <c r="D77">
+        <v>615719.4431780345</v>
       </c>
       <c r="E77">
-        <v>484092</v>
+        <v>-652079.5330276875</v>
       </c>
       <c r="F77">
-        <v>-11161.580769920256</v>
+        <v>36369.68455598247</v>
+      </c>
+      <c r="G77">
+        <v>518043.3154440175</v>
+      </c>
+      <c r="H77">
+        <v>-11944.387239709962</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="C78">
-        <v>-618253.4170074591</v>
+      <c r="D78">
+        <v>-661614.0112440132</v>
+      </c>
+      <c r="E78">
+        <v>518076.46213149617</v>
       </c>
     </row>
     <row r="79">
@@ -5087,16 +6055,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>720222009</v>
+        <v>-995756.966268897</v>
       </c>
       <c r="C101">
-        <v>129898.21950157499</v>
+        <v>770734069.9662689</v>
+      </c>
+      <c r="D101">
+        <v>139008.50313756638</v>
       </c>
       <c r="E101">
-        <v>2441315</v>
+        <v>-1887772.0836769713</v>
       </c>
       <c r="F101">
-        <v>-529282.0940843001</v>
+        <v>1294823.7779033496</v>
+      </c>
+      <c r="G101">
+        <v>2612534.2220966504</v>
+      </c>
+      <c r="H101">
+        <v>-566402.7722511068</v>
       </c>
     </row>
     <row r="102">
@@ -5138,14 +6115,20 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C109">
-        <v>162025.04101176187</v>
+      <c r="D109">
+        <v>173388.50761980377</v>
       </c>
       <c r="E109">
-        <v>1528090</v>
+        <v>-118345.74971185578</v>
       </c>
       <c r="F109">
-        <v>384002.17528252327</v>
+        <v>1294817.9134775028</v>
+      </c>
+      <c r="G109">
+        <v>1635261.0865224972</v>
+      </c>
+      <c r="H109">
+        <v>410933.78948851273</v>
       </c>
     </row>
     <row r="110">
@@ -5153,7 +6136,10 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-73856</v>
+        <v>-1005898.1822103374</v>
+      </c>
+      <c r="C110">
+        <v>-79035.81778966261</v>
       </c>
     </row>
     <row r="111">
@@ -5221,16 +6207,25 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>720295865</v>
+        <v>-770396995.7840586</v>
       </c>
       <c r="C123">
-        <v>-32126.821510186768</v>
+        <v>770813105.7840586</v>
+      </c>
+      <c r="D123">
+        <v>-34380.00448223762</v>
       </c>
       <c r="E123">
-        <v>913225</v>
+        <v>-1769426.3339651155</v>
       </c>
       <c r="F123">
-        <v>-913283.1689447798</v>
+        <v>5.864425846957602</v>
+      </c>
+      <c r="G123">
+        <v>977273.135574153</v>
+      </c>
+      <c r="H123">
+        <v>-977335.3841405585</v>
       </c>
     </row>
     <row r="124">
@@ -5243,16 +6238,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>653615832</v>
+        <v>-145093287.36945856</v>
       </c>
       <c r="C125">
-        <v>-94213080.97999641</v>
+        <v>699456534.3694586</v>
+      </c>
+      <c r="D125">
+        <v>-100820622.58635353</v>
       </c>
       <c r="E125">
-        <v>78949412</v>
+        <v>-55483423.71685065</v>
       </c>
       <c r="F125">
-        <v>233673697.32094243</v>
+        <v>-69070920.22174236</v>
+      </c>
+      <c r="G125">
+        <v>84486451.22174236</v>
+      </c>
+      <c r="H125">
+        <v>250062171.84378764</v>
       </c>
     </row>
     <row r="126">
@@ -5260,10 +6264,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>4441269</v>
-      </c>
-      <c r="E126">
-        <v>-21689534</v>
+        <v>-12608215.025331417</v>
+      </c>
+      <c r="C126">
+        <v>4752753.025331417</v>
+      </c>
+      <c r="F126">
+        <v>-13070213.903613895</v>
+      </c>
+      <c r="G126">
+        <v>-23210708.096386105</v>
       </c>
     </row>
     <row r="127">
@@ -5271,16 +6281,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>658057101</v>
+        <v>-157701502.39479005</v>
       </c>
       <c r="C127">
-        <v>-102104526.564096</v>
+        <v>704209287.39479</v>
+      </c>
+      <c r="D127">
+        <v>-109265526.9310504</v>
       </c>
       <c r="E127">
-        <v>57259878</v>
+        <v>-70675403.62192969</v>
       </c>
       <c r="F127">
-        <v>234519184.5883143</v>
+        <v>-82141134.12535626</v>
+      </c>
+      <c r="G127">
+        <v>61275743.12535625</v>
+      </c>
+      <c r="H127">
+        <v>250966956.52759778</v>
       </c>
     </row>
     <row r="128">
@@ -5288,10 +6307,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>48676278</v>
-      </c>
-      <c r="E128">
-        <v>236318764</v>
+        <v>329.2032202780247</v>
+      </c>
+      <c r="C128">
+        <v>52090140.79677972</v>
+      </c>
+      <c r="F128">
+        <v>1597.3318040072918</v>
+      </c>
+      <c r="G128">
+        <v>252892747.668196</v>
       </c>
     </row>
     <row r="129">
@@ -5299,22 +6324,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>706733379</v>
-      </c>
-      <c r="E129">
-        <v>293578642</v>
+        <v>-157701173.1915698</v>
+      </c>
+      <c r="C129">
+        <v>756299428.1915698</v>
+      </c>
+      <c r="F129">
+        <v>-82139536.79355222</v>
+      </c>
+      <c r="G129">
+        <v>314168490.7935522</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:J129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5324,6 +6355,8 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5331,24 +6364,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -5362,19 +6401,22 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-276920558.9134487</v>
+        <v>-369346112.1819276</v>
       </c>
       <c r="C3">
-        <v>-134290376.9134487</v>
+        <v>-296342109.46293956</v>
       </c>
       <c r="D3">
-        <v>194309587.11362118</v>
-      </c>
-      <c r="F3">
-        <v>205770169.05862767</v>
+        <v>-143708700.18192762</v>
+      </c>
+      <c r="E3">
+        <v>207937298.55254465</v>
       </c>
       <c r="H3">
-        <v>2555030.3236488546</v>
+        <v>220201657.1201496</v>
+      </c>
+      <c r="J3">
+        <v>2734224.8579258774</v>
       </c>
     </row>
     <row r="4">
@@ -5382,19 +6424,22 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>16042664.521558851</v>
+        <v>-25889925.524601102</v>
       </c>
       <c r="C4">
-        <v>-142249564.47844115</v>
+        <v>17167800.990936562</v>
       </c>
       <c r="D4">
-        <v>-118058429.92012227</v>
-      </c>
-      <c r="F4">
-        <v>-105199010.18276146</v>
+        <v>-152226097.5246011</v>
+      </c>
+      <c r="E4">
+        <v>-126338341.57956615</v>
       </c>
       <c r="H4">
-        <v>256328901.3080962</v>
+        <v>-112577039.1093154</v>
+      </c>
+      <c r="J4">
+        <v>274306276.2404016</v>
       </c>
     </row>
     <row r="5">
@@ -5402,19 +6447,22 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>97273191.90160704</v>
+        <v>143133226.25886846</v>
       </c>
       <c r="C5">
-        <v>290626059.90160704</v>
+        <v>104095351.37232319</v>
       </c>
       <c r="D5">
-        <v>259878466.6629898</v>
-      </c>
-      <c r="F5">
-        <v>165014953.72463977</v>
+        <v>311008832.25886846</v>
+      </c>
+      <c r="E5">
+        <v>278104786.864073</v>
       </c>
       <c r="H5">
-        <v>-22357843.54133192</v>
+        <v>176588114.9148375</v>
+      </c>
+      <c r="J5">
+        <v>-23925888.868913762</v>
       </c>
     </row>
     <row r="6">
@@ -5422,19 +6470,22 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>397340.6823303082</v>
+        <v>459052.18277284026</v>
       </c>
       <c r="C6">
-        <v>391842.6823303082</v>
+        <v>425207.7795856593</v>
       </c>
       <c r="D6">
-        <v>401140.14816142886</v>
-      </c>
-      <c r="F6">
-        <v>192065.4623307066</v>
+        <v>419324.18277284026</v>
+      </c>
+      <c r="E6">
+        <v>429273.71720923093</v>
       </c>
       <c r="H6">
-        <v>5287.527910821971</v>
+        <v>205535.78428911715</v>
+      </c>
+      <c r="J6">
+        <v>5658.363471044746</v>
       </c>
     </row>
     <row r="7">
@@ -5467,10 +6518,13 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-1138044.5392686697</v>
+        <v>4460303.126091744</v>
       </c>
       <c r="C12">
-        <v>-4944210.53926867</v>
+        <v>-1217860.1717146765</v>
+      </c>
+      <c r="D12">
+        <v>-5290967.873908256</v>
       </c>
     </row>
     <row r="13">
@@ -5502,17 +6556,20 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C18">
-        <v>119013603.95535406</v>
+      <c r="B18">
+        <v>52642030.80462569</v>
       </c>
       <c r="D18">
-        <v>-32695283.030647174</v>
-      </c>
-      <c r="F18">
-        <v>549479710.119606</v>
+        <v>127360505.80462569</v>
+      </c>
+      <c r="E18">
+        <v>-34988334.49133015</v>
       </c>
       <c r="H18">
-        <v>18703942.77096762</v>
+        <v>588016928.1863331</v>
+      </c>
+      <c r="J18">
+        <v>20015725.36820941</v>
       </c>
     </row>
     <row r="19">
@@ -5525,36 +6582,39 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>52193857.23395288</v>
+        <v>61043299.35781063</v>
       </c>
       <c r="C20">
-        <v>121776846.23395288</v>
+        <v>55854421.98443408</v>
       </c>
       <c r="D20">
-        <v>249417127.3547229</v>
-      </c>
-      <c r="F20">
-        <v>-383512914.43767697</v>
+        <v>130317545.35781063</v>
+      </c>
+      <c r="E20">
+        <v>266909751.83098128</v>
       </c>
       <c r="H20">
-        <v>7232285.078110459</v>
+        <v>-410410214.816382</v>
+      </c>
+      <c r="J20">
+        <v>7739514.266091234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>54387977.56923848</v>
-      </c>
       <c r="D21">
-        <v>48692470.387265325</v>
-      </c>
-      <c r="F21">
-        <v>-1143906.3191979213</v>
+        <v>58202424.78756756</v>
+      </c>
+      <c r="E21">
+        <v>52107468.82117154</v>
       </c>
       <c r="H21">
-        <v>48299357.81789879</v>
+        <v>-1224133.0618036524</v>
+      </c>
+      <c r="J21">
+        <v>51686785.6890864</v>
       </c>
     </row>
     <row r="22">
@@ -5592,19 +6652,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-390236415.3366146</v>
+        <v>-478250262.916195</v>
       </c>
       <c r="C28">
-        <v>-282666872.3366146</v>
+        <v>-417605261.8261993</v>
       </c>
       <c r="D28">
-        <v>52489548.16990954</v>
-      </c>
-      <c r="F28">
-        <v>145954224.4163273</v>
+        <v>-302491434.916195</v>
+      </c>
+      <c r="E28">
+        <v>56170850.91283971</v>
       </c>
       <c r="H28">
-        <v>-231416027.4431154</v>
+        <v>156190580.13702843</v>
+      </c>
+      <c r="J28">
+        <v>-247646162.513562</v>
       </c>
     </row>
     <row r="29">
@@ -5622,19 +6685,22 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-12585954.018412746</v>
+        <v>-5795996.645083629</v>
       </c>
       <c r="C31">
-        <v>-18337730.018412746</v>
+        <v>-13468657.502550123</v>
       </c>
       <c r="D31">
-        <v>-15713232.252109496</v>
-      </c>
-      <c r="F31">
-        <v>718709.8447808257</v>
+        <v>-19623828.64508363</v>
+      </c>
+      <c r="E31">
+        <v>-16815264.31385908</v>
       </c>
       <c r="H31">
-        <v>-3615244.0444581048</v>
+        <v>769115.8515995186</v>
+      </c>
+      <c r="J31">
+        <v>-3868795.6234152094</v>
       </c>
     </row>
     <row r="32">
@@ -5647,19 +6713,22 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-248774.43035172048</v>
+        <v>110045.49002381985</v>
       </c>
       <c r="C33">
-        <v>-73346.43035172047</v>
+        <v>-266221.97990692285</v>
       </c>
       <c r="D33">
-        <v>446958.42071562127</v>
-      </c>
-      <c r="F33">
-        <v>186710.80867533517</v>
+        <v>-78490.50997618012</v>
+      </c>
+      <c r="E33">
+        <v>478305.40916425484</v>
       </c>
       <c r="H33">
-        <v>-442158.3797693142</v>
+        <v>199805.587275568</v>
+      </c>
+      <c r="J33">
+        <v>-473168.72207566025</v>
       </c>
     </row>
     <row r="34">
@@ -5682,19 +6751,22 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-268841321.6555877</v>
+        <v>-298516780.55095667</v>
       </c>
       <c r="C37">
-        <v>-258775787.6555877</v>
+        <v>-287696242.8604732</v>
       </c>
       <c r="D37">
-        <v>-229587522.16158822</v>
-      </c>
-      <c r="F37">
-        <v>-117101245.41382009</v>
+        <v>-276924772.55095667</v>
+      </c>
+      <c r="E37">
+        <v>-245689416.81574166</v>
       </c>
       <c r="H37">
-        <v>-223083966.27094913</v>
+        <v>-125314025.88102862</v>
+      </c>
+      <c r="J37">
+        <v>-238729740.44066802</v>
       </c>
     </row>
     <row r="38">
@@ -5707,19 +6779,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-227679074.95957163</v>
+        <v>-286095932.28407145</v>
       </c>
       <c r="C39">
-        <v>-216280507.95957163</v>
+        <v>-243647122.5496052</v>
       </c>
       <c r="D39">
-        <v>-196092734.09900767</v>
-      </c>
-      <c r="F39">
-        <v>-121849759.09802014</v>
+        <v>-231449128.28407142</v>
+      </c>
+      <c r="E39">
+        <v>-209845504.79481602</v>
       </c>
       <c r="H39">
-        <v>-5731148.75148483</v>
+        <v>-130395571.8937582</v>
+      </c>
+      <c r="J39">
+        <v>-6133097.222267757</v>
       </c>
     </row>
     <row r="40">
@@ -5727,19 +6802,22 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>20191482.49032548</v>
+        <v>27923278.895832807</v>
       </c>
       <c r="C40">
-        <v>43059240.49032548</v>
+        <v>21607592.22011113</v>
       </c>
       <c r="D40">
-        <v>31624337.994086295</v>
-      </c>
-      <c r="F40">
-        <v>2420125.183857115</v>
+        <v>46079157.89583281</v>
+      </c>
+      <c r="E40">
+        <v>33842279.7798325</v>
       </c>
       <c r="H40">
-        <v>362195.11168028414</v>
+        <v>2589858.2790769157</v>
+      </c>
+      <c r="J40">
+        <v>387597.3089670364</v>
       </c>
     </row>
     <row r="41">
@@ -5752,10 +6830,13 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>786796.1053453884</v>
+        <v>1291168.2001639218</v>
       </c>
       <c r="C42">
-        <v>293083.1053453884</v>
+        <v>841977.2749633654</v>
+      </c>
+      <c r="D42">
+        <v>313638.20016392187</v>
       </c>
     </row>
     <row r="43">
@@ -5768,19 +6849,22 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-414452.5501911044</v>
+        <v>-727873.0129857063</v>
       </c>
       <c r="C44">
-        <v>-100663914.5501911</v>
+        <v>-443519.77143854386</v>
       </c>
       <c r="D44">
-        <v>-876047.087894544</v>
-      </c>
-      <c r="F44">
-        <v>82122883.76040092</v>
+        <v>-107723879.0129857</v>
+      </c>
+      <c r="E44">
+        <v>-937487.7872345895</v>
       </c>
       <c r="H44">
-        <v>721869.1564628173</v>
+        <v>87882491.29723638</v>
+      </c>
+      <c r="J44">
+        <v>772496.738493456</v>
       </c>
     </row>
     <row r="45">
@@ -5798,24 +6882,30 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>131090349.8277483</v>
+        <v>119139341.03076094</v>
       </c>
       <c r="C47">
-        <v>298851880.8277483</v>
+        <v>140284242.3495592</v>
       </c>
       <c r="D47">
-        <v>487681236.32343256</v>
-      </c>
-      <c r="F47">
-        <v>310851482.50148696</v>
+        <v>319811563.03076094</v>
+      </c>
+      <c r="E47">
+        <v>521884279.32051843</v>
+      </c>
+      <c r="H47">
+        <v>332652744.9446764</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C48">
-        <v>-31400043.37099551</v>
+      <c r="B48">
+        <v>-36284073.4743488</v>
+      </c>
+      <c r="D48">
+        <v>-33602254.4743488</v>
       </c>
     </row>
     <row r="49">
@@ -5887,14 +6977,14 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="D62">
-        <v>410998.8292338646</v>
-      </c>
-      <c r="F62">
-        <v>707428.3180083497</v>
+      <c r="E62">
+        <v>439823.8271649207</v>
       </c>
       <c r="H62">
-        <v>372423.53455876285</v>
+        <v>757043.1060625465</v>
+      </c>
+      <c r="J62">
+        <v>398543.09220602934</v>
       </c>
     </row>
     <row r="63">
@@ -5918,19 +7008,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>134139.4085666231</v>
+        <v>-584236.5407371359</v>
       </c>
       <c r="C67">
-        <v>618231.4085666231</v>
+        <v>143547.14381884655</v>
       </c>
       <c r="D67">
-        <v>564227.0964435225</v>
-      </c>
-      <c r="F67">
-        <v>-3491507.087968536</v>
+        <v>661590.4592628641</v>
+      </c>
+      <c r="E67">
+        <v>603798.6079194736</v>
       </c>
       <c r="H67">
-        <v>-117509.66815505411</v>
+        <v>-3736380.497400303</v>
+      </c>
+      <c r="J67">
+        <v>-125751.09294880005</v>
       </c>
     </row>
     <row r="68">
@@ -5982,25 +7075,31 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C77">
-        <v>484100.96589230676</v>
+      <c r="B77">
+        <v>-36360.0898496529</v>
       </c>
       <c r="D77">
-        <v>-102427.28365022033</v>
-      </c>
-      <c r="F77">
-        <v>-3491507.087968536</v>
+        <v>518052.9101503471</v>
+      </c>
+      <c r="E77">
+        <v>-109610.9202673974</v>
       </c>
       <c r="H77">
-        <v>-117509.66815505411</v>
+        <v>-3736380.497400303</v>
+      </c>
+      <c r="J77">
+        <v>-125751.09294880005</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="C78">
-        <v>-134130.44267431635</v>
+      <c r="B78">
+        <v>-834951.5491125169</v>
+      </c>
+      <c r="D78">
+        <v>-143537.54911251698</v>
       </c>
     </row>
     <row r="79">
@@ -6114,19 +7213,22 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>719797819.322445</v>
+        <v>767989549.4194607</v>
       </c>
       <c r="C101">
-        <v>2017125.3224450534</v>
+        <v>770280130.1636329</v>
       </c>
       <c r="D101">
-        <v>1357945.0088591783</v>
-      </c>
-      <c r="F101">
-        <v>32653001.514535256</v>
+        <v>2158594.419460595</v>
+      </c>
+      <c r="E101">
+        <v>1453183.144071922</v>
       </c>
       <c r="H101">
-        <v>101934.29457549653</v>
+        <v>34943087.6027457</v>
+      </c>
+      <c r="J101">
+        <v>109083.35588966013</v>
       </c>
     </row>
     <row r="102">
@@ -6168,17 +7270,20 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C109">
-        <v>2789484.04302948</v>
+      <c r="B109">
+        <v>55042.75790794799</v>
       </c>
       <c r="D109">
-        <v>3011461.177300242</v>
-      </c>
-      <c r="F109">
-        <v>405501.12071305997</v>
+        <v>2985121.757907948</v>
+      </c>
+      <c r="E109">
+        <v>3222667.039776657</v>
       </c>
       <c r="H109">
-        <v>101934.29457549653</v>
+        <v>433940.5422739032</v>
+      </c>
+      <c r="J109">
+        <v>109083.35588966013</v>
       </c>
     </row>
     <row r="110">
@@ -6251,16 +7356,19 @@
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>718610281.2794156</v>
+        <v>-1387696.338447353</v>
       </c>
       <c r="C123">
-        <v>-772358.7205844269</v>
+        <v>769009305.310037</v>
       </c>
       <c r="D123">
-        <v>-1653515.06801902</v>
-      </c>
-      <c r="F123">
-        <v>32247500.393822197</v>
+        <v>-826527.3384473531</v>
+      </c>
+      <c r="E123">
+        <v>-1769482.718105674</v>
+      </c>
+      <c r="H123">
+        <v>34509147.060471795</v>
       </c>
     </row>
     <row r="124">
@@ -6273,19 +7381,22 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>443011399.81756294</v>
+        <v>398059200.6967958</v>
       </c>
       <c r="C125">
-        <v>-131655020.18243703</v>
+        <v>474081567.844512</v>
       </c>
       <c r="D125">
-        <v>196231758.1185018</v>
-      </c>
-      <c r="F125">
-        <v>234931662.38477233</v>
+        <v>-140888515.30320418</v>
+      </c>
+      <c r="E125">
+        <v>209994279.12693697</v>
       </c>
       <c r="H125">
-        <v>2539454.9500692966</v>
+        <v>251408363.04789594</v>
+      </c>
+      <c r="J125">
+        <v>2717557.120866737</v>
       </c>
     </row>
     <row r="126">
@@ -6298,19 +7409,22 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>413151265.7697496</v>
+        <v>366566854.44701993</v>
       </c>
       <c r="C127">
-        <v>-187645957.23025042</v>
+        <v>442127222.7164537</v>
       </c>
       <c r="D127">
-        <v>148977753.92215988</v>
-      </c>
-      <c r="F127">
-        <v>233794496.1505804</v>
+        <v>-200806321.5529801</v>
+      </c>
+      <c r="E127">
+        <v>159426161.90566808</v>
       </c>
       <c r="H127">
-        <v>2539454.9500692966</v>
+        <v>250191442.78031915</v>
+      </c>
+      <c r="J127">
+        <v>2717557.120866737</v>
       </c>
     </row>
     <row r="128">
@@ -6325,7 +7439,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>